--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION.xlsx
@@ -356,7 +356,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -516,11 +516,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -729,6 +743,15 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5512,7 +5535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G167"/>
+  <dimension ref="A1:AA167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8.75" customWidth="1" style="73" min="1" max="1"/>
@@ -5522,6 +5545,35 @@
     <col width="61.5" customWidth="1" style="73" min="5" max="5"/>
     <col width="113.75" customWidth="1" style="73" min="6" max="6"/>
     <col width="48.08203125" customWidth="1" style="73" min="7" max="7"/>
+    <col width="8" customWidth="1" style="73" min="8" max="8"/>
+    <col width="8" customWidth="1" style="73" min="9" max="9"/>
+    <col width="8" customWidth="1" style="73" min="10" max="10"/>
+    <col width="8" customWidth="1" style="73" min="11" max="11"/>
+    <col width="8" customWidth="1" style="73" min="12" max="12"/>
+    <col width="8" customWidth="1" style="73" min="13" max="13"/>
+    <col width="8" customWidth="1" style="73" min="14" max="14"/>
+    <col width="8" customWidth="1" style="73" min="15" max="15"/>
+    <col width="8" customWidth="1" style="73" min="16" max="16"/>
+    <col width="8" customWidth="1" style="73" min="17" max="17"/>
+    <col width="8" customWidth="1" style="73" min="18" max="18"/>
+    <col width="8" customWidth="1" style="73" min="19" max="19"/>
+    <col width="8" customWidth="1" style="73" min="20" max="20"/>
+    <col width="8" customWidth="1" style="73" min="21" max="21"/>
+    <col width="8" customWidth="1" style="73" min="22" max="22"/>
+    <col width="8" customWidth="1" style="73" min="23" max="23"/>
+    <col width="8" customWidth="1" style="73" min="24" max="24"/>
+    <col width="8" customWidth="1" style="73" min="25" max="25"/>
+    <col width="8" customWidth="1" style="73" min="26" max="26"/>
+    <col width="8" customWidth="1" style="73" min="27" max="27"/>
+    <col width="8" customWidth="1" style="73" min="28" max="28"/>
+    <col width="8" customWidth="1" style="73" min="29" max="29"/>
+    <col width="8" customWidth="1" style="73" min="30" max="30"/>
+    <col width="8" customWidth="1" style="73" min="31" max="31"/>
+    <col width="8" customWidth="1" style="73" min="32" max="32"/>
+    <col width="8" customWidth="1" style="73" min="33" max="33"/>
+    <col width="8" customWidth="1" style="73" min="34" max="34"/>
+    <col width="8" customWidth="1" style="73" min="35" max="35"/>
+    <col width="8" customWidth="1" style="73" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1" s="73">
@@ -5576,7 +5628,7 @@
       </c>
       <c r="D3" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – MA01</t>
+          <t>Key: MA01 · 6 references in total</t>
         </is>
       </c>
       <c r="E3" s="66" t="n"/>
@@ -5605,7 +5657,7 @@
       </c>
       <c r="D4" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E01</t>
+          <t>Key: E01 · 9 references in total</t>
         </is>
       </c>
       <c r="E4" s="66" t="n"/>
@@ -5663,7 +5715,7 @@
       </c>
       <c r="D6" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E03</t>
+          <t>Key: E03 · 9 references in total</t>
         </is>
       </c>
       <c r="E6" s="66" t="n"/>
@@ -5692,7 +5744,7 @@
       </c>
       <c r="D7" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E03</t>
+          <t>Key: E03 · 10 references in total</t>
         </is>
       </c>
       <c r="E7" s="66" t="n"/>
@@ -5721,7 +5773,7 @@
       </c>
       <c r="D8" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E03</t>
+          <t>Key: E03 · 16 references in total</t>
         </is>
       </c>
       <c r="E8" s="66" t="n"/>
@@ -5750,7 +5802,7 @@
       </c>
       <c r="D9" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E03</t>
+          <t>Key: E03 · 16 references in total</t>
         </is>
       </c>
       <c r="E9" s="66" t="n"/>
@@ -5779,7 +5831,7 @@
       </c>
       <c r="D10" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E03</t>
+          <t>Key: E03 · 7 references in total</t>
         </is>
       </c>
       <c r="E10" s="66" t="n"/>
@@ -5808,7 +5860,7 @@
       </c>
       <c r="D11" s="65" t="inlineStr">
         <is>
-          <t>5 file(s) – BLA06, DMA01, DMA02, DMA03, DMA04</t>
+          <t>Key: BLA06, DMA01, DMA02, DMA03, DMA04 · 14 references in total</t>
         </is>
       </c>
       <c r="E11" s="66" t="n"/>
@@ -5837,7 +5889,7 @@
       </c>
       <c r="D12" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E03</t>
+          <t>Key: E03 · 6 references in total</t>
         </is>
       </c>
       <c r="E12" s="66" t="n"/>
@@ -5866,7 +5918,7 @@
       </c>
       <c r="D13" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E01</t>
+          <t>Key: E01 · 8 references in total</t>
         </is>
       </c>
       <c r="E13" s="66" t="n"/>
@@ -5895,7 +5947,7 @@
       </c>
       <c r="D14" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – E05</t>
+          <t>Key: E05 · 11 references in total</t>
         </is>
       </c>
       <c r="E14" s="66" t="n"/>
@@ -5924,7 +5976,7 @@
       </c>
       <c r="D15" s="65" t="inlineStr">
         <is>
-          <t>1 file(s) – MA01</t>
+          <t>Key: MA01 · 6 references in total</t>
         </is>
       </c>
       <c r="E15" s="66" t="n"/>
@@ -5953,7 +6005,7 @@
       </c>
       <c r="D16" s="65" t="inlineStr">
         <is>
-          <t>5 file(s) – BLA06, DMA01, DMA02, DMA03, DMA04</t>
+          <t>Key: BLA06, DMA01, DMA02, DMA03, DMA04 · 20 references in total</t>
         </is>
       </c>
       <c r="E16" s="66" t="n"/>
@@ -6093,6 +6145,11 @@
       <c r="G22" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H22" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (6) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -6152,6 +6209,36 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H23" s="90" t="inlineStr">
+        <is>
+          <t>MA01</t>
+        </is>
+      </c>
+      <c r="I23" s="91" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="J23" s="91" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="K23" s="91" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="L23" s="91" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="M23" s="91" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="73"/>
     <row r="25" ht="15.5" customHeight="1" s="73">
@@ -6195,6 +6282,11 @@
       <c r="G26" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H26" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (9) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -6246,6 +6338,51 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H27" s="91" t="inlineStr">
+        <is>
+          <t>BLA01</t>
+        </is>
+      </c>
+      <c r="I27" s="91" t="inlineStr">
+        <is>
+          <t>BLA02</t>
+        </is>
+      </c>
+      <c r="J27" s="91" t="inlineStr">
+        <is>
+          <t>BLA03</t>
+        </is>
+      </c>
+      <c r="K27" s="91" t="inlineStr">
+        <is>
+          <t>BLA04</t>
+        </is>
+      </c>
+      <c r="L27" s="91" t="inlineStr">
+        <is>
+          <t>BLA05</t>
+        </is>
+      </c>
+      <c r="M27" s="91" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="N27" s="90" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="O27" s="91" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="P27" s="91" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="73"/>
     <row r="29" s="73"/>
@@ -6290,6 +6427,11 @@
       <c r="G31" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H31" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (9) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -6340,6 +6482,51 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H32" s="91" t="inlineStr">
+        <is>
+          <t>BLA01</t>
+        </is>
+      </c>
+      <c r="I32" s="91" t="inlineStr">
+        <is>
+          <t>BLA02</t>
+        </is>
+      </c>
+      <c r="J32" s="91" t="inlineStr">
+        <is>
+          <t>BLA03</t>
+        </is>
+      </c>
+      <c r="K32" s="91" t="inlineStr">
+        <is>
+          <t>BLA04</t>
+        </is>
+      </c>
+      <c r="L32" s="91" t="inlineStr">
+        <is>
+          <t>BLA05</t>
+        </is>
+      </c>
+      <c r="M32" s="90" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="N32" s="91" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="O32" s="91" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="P32" s="91" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
     </row>
     <row r="33" s="73"/>
     <row r="34" ht="15.5" customHeight="1" s="73">
@@ -6383,6 +6570,11 @@
       <c r="G35" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H35" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (10) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -6433,6 +6625,56 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H36" s="91" t="inlineStr">
+        <is>
+          <t>BLA01</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="inlineStr">
+        <is>
+          <t>BLA02</t>
+        </is>
+      </c>
+      <c r="J36" s="91" t="inlineStr">
+        <is>
+          <t>BLA03</t>
+        </is>
+      </c>
+      <c r="K36" s="91" t="inlineStr">
+        <is>
+          <t>BLA04</t>
+        </is>
+      </c>
+      <c r="L36" s="91" t="inlineStr">
+        <is>
+          <t>BLA05</t>
+        </is>
+      </c>
+      <c r="M36" s="90" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="N36" s="91" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="O36" s="91" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="P36" s="91" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="Q36" s="91" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
     </row>
     <row r="37" s="73"/>
     <row r="38" ht="15.5" customHeight="1" s="73">
@@ -6476,6 +6718,11 @@
       <c r="G39" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H39" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (16) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -6526,6 +6773,86 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H40" s="91" t="inlineStr">
+        <is>
+          <t>BLA06</t>
+        </is>
+      </c>
+      <c r="I40" s="91" t="inlineStr">
+        <is>
+          <t>DMA01</t>
+        </is>
+      </c>
+      <c r="J40" s="91" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="K40" s="91" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="L40" s="91" t="inlineStr">
+        <is>
+          <t>DMA04</t>
+        </is>
+      </c>
+      <c r="M40" s="91" t="inlineStr">
+        <is>
+          <t>DMA05</t>
+        </is>
+      </c>
+      <c r="N40" s="91" t="inlineStr">
+        <is>
+          <t>DMA06</t>
+        </is>
+      </c>
+      <c r="O40" s="91" t="inlineStr">
+        <is>
+          <t>DMA07</t>
+        </is>
+      </c>
+      <c r="P40" s="91" t="inlineStr">
+        <is>
+          <t>DMA08</t>
+        </is>
+      </c>
+      <c r="Q40" s="91" t="inlineStr">
+        <is>
+          <t>DMA09</t>
+        </is>
+      </c>
+      <c r="R40" s="91" t="inlineStr">
+        <is>
+          <t>DMA10</t>
+        </is>
+      </c>
+      <c r="S40" s="91" t="inlineStr">
+        <is>
+          <t>DMA11</t>
+        </is>
+      </c>
+      <c r="T40" s="91" t="inlineStr">
+        <is>
+          <t>DMA12</t>
+        </is>
+      </c>
+      <c r="U40" s="90" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="V40" s="91" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="W40" s="91" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
     </row>
     <row r="41" s="73"/>
     <row r="42" ht="15.5" customHeight="1" s="73">
@@ -6569,6 +6896,11 @@
       <c r="G43" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H43" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (16) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -6619,6 +6951,86 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H44" s="91" t="inlineStr">
+        <is>
+          <t>BLA06</t>
+        </is>
+      </c>
+      <c r="I44" s="91" t="inlineStr">
+        <is>
+          <t>DMA01</t>
+        </is>
+      </c>
+      <c r="J44" s="91" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="K44" s="91" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="L44" s="91" t="inlineStr">
+        <is>
+          <t>DMA04</t>
+        </is>
+      </c>
+      <c r="M44" s="91" t="inlineStr">
+        <is>
+          <t>DMA05</t>
+        </is>
+      </c>
+      <c r="N44" s="91" t="inlineStr">
+        <is>
+          <t>DMA06</t>
+        </is>
+      </c>
+      <c r="O44" s="91" t="inlineStr">
+        <is>
+          <t>DMA07</t>
+        </is>
+      </c>
+      <c r="P44" s="91" t="inlineStr">
+        <is>
+          <t>DMA08</t>
+        </is>
+      </c>
+      <c r="Q44" s="91" t="inlineStr">
+        <is>
+          <t>DMA09</t>
+        </is>
+      </c>
+      <c r="R44" s="91" t="inlineStr">
+        <is>
+          <t>DMA10</t>
+        </is>
+      </c>
+      <c r="S44" s="91" t="inlineStr">
+        <is>
+          <t>DMA11</t>
+        </is>
+      </c>
+      <c r="T44" s="91" t="inlineStr">
+        <is>
+          <t>DMA12</t>
+        </is>
+      </c>
+      <c r="U44" s="90" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="V44" s="91" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="W44" s="91" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="73"/>
     <row r="46" ht="15.5" customHeight="1" s="73">
@@ -6662,6 +7074,11 @@
       <c r="G47" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H47" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (7) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -6712,6 +7129,41 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H48" s="91" t="inlineStr">
+        <is>
+          <t>BLA01</t>
+        </is>
+      </c>
+      <c r="I48" s="91" t="inlineStr">
+        <is>
+          <t>BLA02</t>
+        </is>
+      </c>
+      <c r="J48" s="91" t="inlineStr">
+        <is>
+          <t>BLA03</t>
+        </is>
+      </c>
+      <c r="K48" s="91" t="inlineStr">
+        <is>
+          <t>BLA04</t>
+        </is>
+      </c>
+      <c r="L48" s="91" t="inlineStr">
+        <is>
+          <t>BLA05</t>
+        </is>
+      </c>
+      <c r="M48" s="90" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="N48" s="91" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="73"/>
     <row r="50" ht="15.5" customHeight="1" s="73">
@@ -6757,6 +7209,11 @@
           <t>Control Sample Assessment Result (Pass/Fail)</t>
         </is>
       </c>
+      <c r="H51" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (14) – click to open; key evidence in green</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="90" customHeight="1" s="73">
       <c r="A52" s="69" t="inlineStr">
@@ -6795,6 +7252,76 @@
       <c r="G52" s="67" t="inlineStr">
         <is>
           <t>PASS</t>
+        </is>
+      </c>
+      <c r="H52" s="90" t="inlineStr">
+        <is>
+          <t>BLA06</t>
+        </is>
+      </c>
+      <c r="I52" s="90" t="inlineStr">
+        <is>
+          <t>DMA01</t>
+        </is>
+      </c>
+      <c r="J52" s="90" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="K52" s="90" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="L52" s="90" t="inlineStr">
+        <is>
+          <t>DMA04</t>
+        </is>
+      </c>
+      <c r="M52" s="91" t="inlineStr">
+        <is>
+          <t>DMA05</t>
+        </is>
+      </c>
+      <c r="N52" s="91" t="inlineStr">
+        <is>
+          <t>DMA06</t>
+        </is>
+      </c>
+      <c r="O52" s="91" t="inlineStr">
+        <is>
+          <t>DMA07</t>
+        </is>
+      </c>
+      <c r="P52" s="91" t="inlineStr">
+        <is>
+          <t>DMA08</t>
+        </is>
+      </c>
+      <c r="Q52" s="91" t="inlineStr">
+        <is>
+          <t>DMA09</t>
+        </is>
+      </c>
+      <c r="R52" s="91" t="inlineStr">
+        <is>
+          <t>DMA10</t>
+        </is>
+      </c>
+      <c r="S52" s="91" t="inlineStr">
+        <is>
+          <t>DMA11</t>
+        </is>
+      </c>
+      <c r="T52" s="91" t="inlineStr">
+        <is>
+          <t>DMA12</t>
+        </is>
+      </c>
+      <c r="U52" s="91" t="inlineStr">
+        <is>
+          <t>E09</t>
         </is>
       </c>
     </row>
@@ -7007,6 +7534,11 @@
       <c r="G59" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H59" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (6) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -7057,6 +7589,36 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H60" s="91" t="inlineStr">
+        <is>
+          <t>MA01</t>
+        </is>
+      </c>
+      <c r="I60" s="91" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="J60" s="91" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="K60" s="90" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="L60" s="91" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="M60" s="91" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
     </row>
     <row r="61" s="73"/>
     <row r="62" ht="15.5" customHeight="1" s="73">
@@ -7100,6 +7662,11 @@
       <c r="G63" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H63" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (8) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -7151,6 +7718,46 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H64" s="91" t="inlineStr">
+        <is>
+          <t>BLA01</t>
+        </is>
+      </c>
+      <c r="I64" s="91" t="inlineStr">
+        <is>
+          <t>BLA02</t>
+        </is>
+      </c>
+      <c r="J64" s="91" t="inlineStr">
+        <is>
+          <t>BLA03</t>
+        </is>
+      </c>
+      <c r="K64" s="91" t="inlineStr">
+        <is>
+          <t>BLA04</t>
+        </is>
+      </c>
+      <c r="L64" s="91" t="inlineStr">
+        <is>
+          <t>BLA05</t>
+        </is>
+      </c>
+      <c r="M64" s="91" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="N64" s="90" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="O64" s="91" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
     </row>
     <row r="65" s="73"/>
     <row r="66" ht="15.5" customHeight="1" s="73">
@@ -7194,6 +7801,11 @@
       <c r="G67" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H67" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (11) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -7244,6 +7856,61 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H68" s="91" t="inlineStr">
+        <is>
+          <t>BLA01</t>
+        </is>
+      </c>
+      <c r="I68" s="91" t="inlineStr">
+        <is>
+          <t>BLA02</t>
+        </is>
+      </c>
+      <c r="J68" s="91" t="inlineStr">
+        <is>
+          <t>BLA03</t>
+        </is>
+      </c>
+      <c r="K68" s="91" t="inlineStr">
+        <is>
+          <t>BLA04</t>
+        </is>
+      </c>
+      <c r="L68" s="91" t="inlineStr">
+        <is>
+          <t>BLA05</t>
+        </is>
+      </c>
+      <c r="M68" s="91" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="N68" s="91" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="O68" s="90" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="P68" s="91" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="Q68" s="91" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="R68" s="91" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
     </row>
     <row r="69" s="73"/>
     <row r="70" ht="15.5" customHeight="1" s="73">
@@ -7287,6 +7954,11 @@
       <c r="G71" s="62" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H71" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (6) – click to open; key evidence in green</t>
         </is>
       </c>
     </row>
@@ -7346,6 +8018,36 @@
           <t>PASS</t>
         </is>
       </c>
+      <c r="H72" s="91" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="I72" s="90" t="inlineStr">
+        <is>
+          <t>MA01</t>
+        </is>
+      </c>
+      <c r="J72" s="91" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="K72" s="91" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="L72" s="91" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="M72" s="91" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
     </row>
     <row r="73" s="73"/>
     <row r="74" ht="15.5" customHeight="1" s="73">
@@ -7391,6 +8093,11 @@
           <t>Control Sample Assessment Result (Pass/Fail)</t>
         </is>
       </c>
+      <c r="H75" s="89" t="inlineStr">
+        <is>
+          <t>All references for this attribute (20) – click to open; key evidence in green</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="78" customHeight="1" s="73">
       <c r="A76" s="69" t="inlineStr">
@@ -7429,6 +8136,106 @@
       <c r="G76" s="67" t="inlineStr">
         <is>
           <t>PASS</t>
+        </is>
+      </c>
+      <c r="H76" s="91" t="inlineStr">
+        <is>
+          <t>BLA01</t>
+        </is>
+      </c>
+      <c r="I76" s="91" t="inlineStr">
+        <is>
+          <t>BLA02</t>
+        </is>
+      </c>
+      <c r="J76" s="91" t="inlineStr">
+        <is>
+          <t>BLA03</t>
+        </is>
+      </c>
+      <c r="K76" s="91" t="inlineStr">
+        <is>
+          <t>BLA04</t>
+        </is>
+      </c>
+      <c r="L76" s="91" t="inlineStr">
+        <is>
+          <t>BLA05</t>
+        </is>
+      </c>
+      <c r="M76" s="90" t="inlineStr">
+        <is>
+          <t>BLA06</t>
+        </is>
+      </c>
+      <c r="N76" s="90" t="inlineStr">
+        <is>
+          <t>DMA01</t>
+        </is>
+      </c>
+      <c r="O76" s="90" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="P76" s="90" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="Q76" s="90" t="inlineStr">
+        <is>
+          <t>DMA04</t>
+        </is>
+      </c>
+      <c r="R76" s="91" t="inlineStr">
+        <is>
+          <t>DMA05</t>
+        </is>
+      </c>
+      <c r="S76" s="91" t="inlineStr">
+        <is>
+          <t>DMA06</t>
+        </is>
+      </c>
+      <c r="T76" s="91" t="inlineStr">
+        <is>
+          <t>DMA07</t>
+        </is>
+      </c>
+      <c r="U76" s="91" t="inlineStr">
+        <is>
+          <t>DMA08</t>
+        </is>
+      </c>
+      <c r="V76" s="91" t="inlineStr">
+        <is>
+          <t>DMA09</t>
+        </is>
+      </c>
+      <c r="W76" s="91" t="inlineStr">
+        <is>
+          <t>DMA10</t>
+        </is>
+      </c>
+      <c r="X76" s="91" t="inlineStr">
+        <is>
+          <t>DMA11</t>
+        </is>
+      </c>
+      <c r="Y76" s="91" t="inlineStr">
+        <is>
+          <t>DMA12</t>
+        </is>
+      </c>
+      <c r="Z76" s="91" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="AA76" s="91" t="inlineStr">
+        <is>
+          <t>E09</t>
         </is>
       </c>
     </row>
@@ -10713,25 +11520,38 @@
     <row r="278" s="73"/>
     <row r="279" s="73"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="32">
+    <mergeCell ref="H59:M59"/>
+    <mergeCell ref="H47:N47"/>
     <mergeCell ref="A122:G122"/>
     <mergeCell ref="A91:G91"/>
+    <mergeCell ref="H67:R67"/>
     <mergeCell ref="A62:G62"/>
     <mergeCell ref="A156:G156"/>
     <mergeCell ref="A38:G38"/>
+    <mergeCell ref="H63:O63"/>
     <mergeCell ref="A58:G58"/>
     <mergeCell ref="A34:G34"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="H35:Q35"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A82:G82"/>
+    <mergeCell ref="H51:U51"/>
     <mergeCell ref="A107:G107"/>
+    <mergeCell ref="H43:W43"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="H71:M71"/>
     <mergeCell ref="A70:G70"/>
+    <mergeCell ref="H39:W39"/>
     <mergeCell ref="A25:G25"/>
+    <mergeCell ref="H26:P26"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="A74:G74"/>
+    <mergeCell ref="H75:AA75"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A50:G50"/>
+    <mergeCell ref="H31:P31"/>
     <mergeCell ref="A42:G42"/>
   </mergeCells>
   <hyperlinks>
@@ -10753,22 +11573,160 @@
     <hyperlink ref="B18" location="'Application Attribute Testing'!A122" display="Evidence reference table – evidence number → attribute tests"/>
     <hyperlink ref="B19" location="'Application Attribute Testing'!A156" display="Conclusion – all applications in scope (PASS) with evidence references"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink ref="H23" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink ref="I23" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink ref="J23" location="'Application Attribute Testing'!A111" display="E02"/>
+    <hyperlink ref="K23" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="L23" location="'Application Attribute Testing'!A113" display="E04"/>
+    <hyperlink ref="M23" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink ref="H27" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink ref="I27" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink ref="J27" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink ref="K27" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink ref="L27" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink ref="M27" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink ref="N27" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink ref="O27" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="P27" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="H32" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink ref="I32" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink ref="J32" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink ref="K32" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink ref="L32" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink ref="M32" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="N32" location="'Application Attribute Testing'!A113" display="E04"/>
+    <hyperlink ref="O32" location="'Application Attribute Testing'!A117" display="E09"/>
+    <hyperlink ref="P32" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A36" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="H36" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink ref="I36" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink ref="J36" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink ref="K36" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink ref="L36" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink ref="M36" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="N36" location="'Application Attribute Testing'!A113" display="E04"/>
+    <hyperlink ref="O36" location="'Application Attribute Testing'!A115" display="E07"/>
+    <hyperlink ref="P36" location="'Application Attribute Testing'!A116" display="E08"/>
+    <hyperlink ref="Q36" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A40" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="H40" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink ref="I40" location="'Application Attribute Testing'!A93" display="DMA01"/>
+    <hyperlink ref="J40" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink ref="K40" location="'Application Attribute Testing'!A95" display="DMA03"/>
+    <hyperlink ref="L40" location="'Application Attribute Testing'!A96" display="DMA04"/>
+    <hyperlink ref="M40" location="'Application Attribute Testing'!A97" display="DMA05"/>
+    <hyperlink ref="N40" location="'Application Attribute Testing'!A98" display="DMA06"/>
+    <hyperlink ref="O40" location="'Application Attribute Testing'!A99" display="DMA07"/>
+    <hyperlink ref="P40" location="'Application Attribute Testing'!A100" display="DMA08"/>
+    <hyperlink ref="Q40" location="'Application Attribute Testing'!A101" display="DMA09"/>
+    <hyperlink ref="R40" location="'Application Attribute Testing'!A102" display="DMA10"/>
+    <hyperlink ref="S40" location="'Application Attribute Testing'!A103" display="DMA11"/>
+    <hyperlink ref="T40" location="'Application Attribute Testing'!A104" display="DMA12"/>
+    <hyperlink ref="U40" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="V40" location="'Application Attribute Testing'!A113" display="E04"/>
+    <hyperlink ref="W40" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A44" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="H44" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink ref="I44" location="'Application Attribute Testing'!A93" display="DMA01"/>
+    <hyperlink ref="J44" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink ref="K44" location="'Application Attribute Testing'!A95" display="DMA03"/>
+    <hyperlink ref="L44" location="'Application Attribute Testing'!A96" display="DMA04"/>
+    <hyperlink ref="M44" location="'Application Attribute Testing'!A97" display="DMA05"/>
+    <hyperlink ref="N44" location="'Application Attribute Testing'!A98" display="DMA06"/>
+    <hyperlink ref="O44" location="'Application Attribute Testing'!A99" display="DMA07"/>
+    <hyperlink ref="P44" location="'Application Attribute Testing'!A100" display="DMA08"/>
+    <hyperlink ref="Q44" location="'Application Attribute Testing'!A101" display="DMA09"/>
+    <hyperlink ref="R44" location="'Application Attribute Testing'!A102" display="DMA10"/>
+    <hyperlink ref="S44" location="'Application Attribute Testing'!A103" display="DMA11"/>
+    <hyperlink ref="T44" location="'Application Attribute Testing'!A104" display="DMA12"/>
+    <hyperlink ref="U44" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="V44" location="'Application Attribute Testing'!A113" display="E04"/>
+    <hyperlink ref="W44" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A48" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="H48" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink ref="I48" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink ref="J48" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink ref="K48" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink ref="L48" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink ref="M48" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="N48" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A52" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink ref="H52" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink ref="I52" location="'Application Attribute Testing'!A93" display="DMA01"/>
+    <hyperlink ref="J52" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink ref="K52" location="'Application Attribute Testing'!A95" display="DMA03"/>
+    <hyperlink ref="L52" location="'Application Attribute Testing'!A96" display="DMA04"/>
+    <hyperlink ref="M52" location="'Application Attribute Testing'!A97" display="DMA05"/>
+    <hyperlink ref="N52" location="'Application Attribute Testing'!A98" display="DMA06"/>
+    <hyperlink ref="O52" location="'Application Attribute Testing'!A99" display="DMA07"/>
+    <hyperlink ref="P52" location="'Application Attribute Testing'!A100" display="DMA08"/>
+    <hyperlink ref="Q52" location="'Application Attribute Testing'!A101" display="DMA09"/>
+    <hyperlink ref="R52" location="'Application Attribute Testing'!A102" display="DMA10"/>
+    <hyperlink ref="S52" location="'Application Attribute Testing'!A103" display="DMA11"/>
+    <hyperlink ref="T52" location="'Application Attribute Testing'!A104" display="DMA12"/>
+    <hyperlink ref="U52" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A53" location="'Application Attribute Testing'!A93" display="DMA01"/>
     <hyperlink ref="A54" location="'Application Attribute Testing'!A94" display="DMA02"/>
     <hyperlink ref="A55" location="'Application Attribute Testing'!A95" display="DMA03"/>
     <hyperlink ref="A56" location="'Application Attribute Testing'!A96" display="DMA04"/>
     <hyperlink ref="A60" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="H60" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink ref="I60" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink ref="J60" location="'Application Attribute Testing'!A111" display="E02"/>
+    <hyperlink ref="K60" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="L60" location="'Application Attribute Testing'!A113" display="E04"/>
+    <hyperlink ref="M60" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A64" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink ref="H64" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink ref="I64" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink ref="J64" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink ref="K64" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink ref="L64" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink ref="M64" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink ref="N64" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink ref="O64" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="A68" location="'Application Attribute Testing'!A114" display="E05"/>
+    <hyperlink ref="H68" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink ref="I68" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink ref="J68" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink ref="K68" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink ref="L68" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink ref="M68" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink ref="N68" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="O68" location="'Application Attribute Testing'!A114" display="E05"/>
+    <hyperlink ref="P68" location="'Application Attribute Testing'!A116" display="E08"/>
+    <hyperlink ref="Q68" location="'Application Attribute Testing'!A117" display="E09"/>
+    <hyperlink ref="R68" location="'Application Attribute Testing'!A118" display="E10"/>
     <hyperlink ref="A72" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink ref="H72" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink ref="I72" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink ref="J72" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink ref="K72" location="'Application Attribute Testing'!A111" display="E02"/>
+    <hyperlink ref="L72" location="'Application Attribute Testing'!A114" display="E05"/>
+    <hyperlink ref="M72" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A76" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink ref="H76" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink ref="I76" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink ref="J76" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink ref="K76" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink ref="L76" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink ref="M76" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink ref="N76" location="'Application Attribute Testing'!A93" display="DMA01"/>
+    <hyperlink ref="O76" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink ref="P76" location="'Application Attribute Testing'!A95" display="DMA03"/>
+    <hyperlink ref="Q76" location="'Application Attribute Testing'!A96" display="DMA04"/>
+    <hyperlink ref="R76" location="'Application Attribute Testing'!A97" display="DMA05"/>
+    <hyperlink ref="S76" location="'Application Attribute Testing'!A98" display="DMA06"/>
+    <hyperlink ref="T76" location="'Application Attribute Testing'!A99" display="DMA07"/>
+    <hyperlink ref="U76" location="'Application Attribute Testing'!A100" display="DMA08"/>
+    <hyperlink ref="V76" location="'Application Attribute Testing'!A101" display="DMA09"/>
+    <hyperlink ref="W76" location="'Application Attribute Testing'!A102" display="DMA10"/>
+    <hyperlink ref="X76" location="'Application Attribute Testing'!A103" display="DMA11"/>
+    <hyperlink ref="Y76" location="'Application Attribute Testing'!A104" display="DMA12"/>
+    <hyperlink ref="Z76" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink ref="AA76" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A77" location="'Application Attribute Testing'!A93" display="DMA01"/>
     <hyperlink ref="A78" location="'Application Attribute Testing'!A94" display="DMA02"/>
     <hyperlink ref="A79" location="'Application Attribute Testing'!A95" display="DMA03"/>

--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION.xlsx
@@ -2059,7 +2059,6 @@
       </c>
     </row>
     <row r="2"/>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1" s="73">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -2414,7 +2413,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
@@ -2436,7 +2434,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="77" t="inlineStr">
         <is>
@@ -4902,7 +4899,6 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="33.15" customHeight="1" s="73">
       <c r="A16" s="50" t="inlineStr">
         <is>
@@ -5265,59 +5261,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
     <row r="79" ht="75" customHeight="1" s="73">
       <c r="A79" s="85" t="inlineStr">
         <is>
@@ -11000,7 +10943,7 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="26" customHeight="1" s="73">
+    <row r="157" ht="40" customHeight="1" s="73">
       <c r="A157" s="62" t="inlineStr">
         <is>
           <t>App ID</t>
@@ -11018,12 +10961,12 @@
       </c>
       <c r="D157" s="62" t="inlineStr">
         <is>
-          <t>Evidence references (click App ID for full detail)</t>
+          <t>Evidence references → attributes they support (column letters; click App ID for full detail)</t>
         </is>
       </c>
       <c r="E157" s="62" t="inlineStr">
         <is>
-          <t>Attributes tested</t>
+          <t>Attributes tested → evidence references (PASS)</t>
         </is>
       </c>
       <c r="F157" s="62" t="inlineStr">
@@ -11037,7 +10980,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="124" customHeight="1" s="73">
+    <row r="158" ht="258" customHeight="1" s="73">
       <c r="A158" s="70" t="inlineStr">
         <is>
           <t>1822</t>
@@ -11055,12 +10998,36 @@
       </c>
       <c r="D158" s="65" t="inlineStr">
         <is>
-          <t>BLA01, DMA01, DMA02, MA01, E01, E02, E03, E04, E05, E09, E16b</t>
+          <t>BLA01 → B, E, F, I, L, M, O
+DMA01 → G, H, J, O
+DMA02 → B, C, L, M, N
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, K
+E05 → M, N
+E09 → E, G, H, J, M, N, O
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E158" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA01, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA01, E03, E09, E16b
+F Business Data validation – PASS → BLA01, E03, E16b
+G Business line manager name – PASS → DMA01, E03, E09
+H Business line manager approval dates – PASS → DMA01, E03, E09
+I DIV Test procedures listed within the Test results document – PASS → BLA01, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → DMA01, E09
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA01, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA01, DMA02, E03, E05, E09
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05, E09
+O Business Line Approval of Results – PASS → BLA01, DMA01, E03, E09</t>
         </is>
       </c>
       <c r="F158" s="65" t="inlineStr">
@@ -11074,7 +11041,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="124" customHeight="1" s="73">
+    <row r="159" ht="258" customHeight="1" s="73">
       <c r="A159" s="70" t="inlineStr">
         <is>
           <t>1867</t>
@@ -11092,12 +11059,36 @@
       </c>
       <c r="D159" s="65" t="inlineStr">
         <is>
-          <t>BLA01, DMA01, DMA02, MA01, E01, E02, E03, E04, E05, E09, E16b</t>
+          <t>BLA01 → B, E, F, I, L, M, O
+DMA01 → G, H, J, O
+DMA02 → B, C, L, M, N
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, E, F, G, H, K
+E05 → M, N
+E09 → E, G, H, J, M, N, O
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E159" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA01, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA01, E03, E04, E09, E16b
+F Business Data validation – PASS → BLA01, E03, E04, E16b
+G Business line manager name – PASS → DMA01, E03, E04, E09
+H Business line manager approval dates – PASS → DMA01, E03, E04, E09
+I DIV Test procedures listed within the Test results document – PASS → BLA01, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → DMA01, E09
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA01, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA01, DMA02, E03, E05, E09
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05, E09
+O Business Line Approval of Results – PASS → BLA01, DMA01, E03, E09</t>
         </is>
       </c>
       <c r="F159" s="65" t="inlineStr">
@@ -11111,7 +11102,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="124" customHeight="1" s="73">
+    <row r="160" ht="258" customHeight="1" s="73">
       <c r="A160" s="70" t="inlineStr">
         <is>
           <t>1868</t>
@@ -11129,12 +11120,36 @@
       </c>
       <c r="D160" s="65" t="inlineStr">
         <is>
-          <t>BLA01, DMA01, DMA02, MA01, E01, E02, E03, E04, E05, E09, E16b</t>
+          <t>BLA01 → B, E, F, I, L, M, O
+DMA01 → G, H, J, O
+DMA02 → B, C, L, M, N
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, E, F, G, H, K
+E05 → M, N
+E09 → E, G, H, J, M, N, O
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E160" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA01, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA01, E03, E04, E09, E16b
+F Business Data validation – PASS → BLA01, E03, E04, E16b
+G Business line manager name – PASS → DMA01, E03, E04, E09
+H Business line manager approval dates – PASS → DMA01, E03, E04, E09
+I DIV Test procedures listed within the Test results document – PASS → BLA01, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → DMA01, E09
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA01, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA01, DMA02, E03, E05, E09
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05, E09
+O Business Line Approval of Results – PASS → BLA01, DMA01, E03, E09</t>
         </is>
       </c>
       <c r="F160" s="65" t="inlineStr">
@@ -11148,7 +11163,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="124" customHeight="1" s="73">
+    <row r="161" ht="294" customHeight="1" s="73">
       <c r="A161" s="70" t="inlineStr">
         <is>
           <t>3299</t>
@@ -11166,12 +11181,39 @@
       </c>
       <c r="D161" s="65" t="inlineStr">
         <is>
-          <t>BLA01, BLA02, DMA01, DMA02, DMA05, DMA11, MA01, E01, E02, E03, E04, E05, E09, E16b</t>
+          <t>BLA01 → B, E, F, I, L, M, O
+BLA02 → B, E, F, I, L, M, O
+DMA01 → G, H, J, O
+DMA02 → B, C, G, H, J, L, M, N, O
+DMA05 → G, H, J, O
+DMA11 → G, H, J, O
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, E, F, G, H, K
+E05 → M, N
+E09 → E, G, H, J, M, N, O
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E161" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA01, BLA02, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA01, BLA02, E03, E04, E09, E16b
+F Business Data validation – PASS → BLA01, BLA02, E03, E04, E16b
+G Business line manager name – PASS → DMA01, DMA02, DMA05, DMA11, E03, E04, E09
+H Business line manager approval dates – PASS → DMA01, DMA02, DMA05, DMA11, E03, E04, E09
+I DIV Test procedures listed within the Test results document – PASS → BLA01, BLA02, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → DMA01, DMA02, DMA05, DMA11, E09
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA01, BLA02, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA01, BLA02, DMA02, E03, E05, E09
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05, E09
+O Business Line Approval of Results – PASS → BLA01, BLA02, DMA01, DMA02, DMA05, DMA11, E03, E09</t>
         </is>
       </c>
       <c r="F161" s="65" t="inlineStr">
@@ -11185,7 +11227,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="124" customHeight="1" s="73">
+    <row r="162" ht="246" customHeight="1" s="73">
       <c r="A162" s="70" t="inlineStr">
         <is>
           <t>4052</t>
@@ -11203,12 +11245,35 @@
       </c>
       <c r="D162" s="65" t="inlineStr">
         <is>
-          <t>BLA04, DMA02, DMA04, MA01, E01, E02, E03, E04, E05, E16b</t>
+          <t>BLA04 → B, E, F, I, L, M, O
+DMA02 → B, C, L, M, N
+DMA04 → G, H, J, O
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, K
+E05 → M, N
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E162" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA04, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA04, E03, E16b
+F Business Data validation – PASS → BLA04, E03, E16b
+G Business line manager name – PASS → DMA04, E03
+H Business line manager approval dates – PASS → DMA04, E03
+I DIV Test procedures listed within the Test results document – PASS → BLA04, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → DMA04
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA04, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA04, DMA02, E03, E05
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05
+O Business Line Approval of Results – PASS → BLA04, DMA04, E03</t>
         </is>
       </c>
       <c r="F162" s="65" t="inlineStr">
@@ -11222,7 +11287,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="124" customHeight="1" s="73">
+    <row r="163" ht="246" customHeight="1" s="73">
       <c r="A163" s="70" t="inlineStr">
         <is>
           <t>3301</t>
@@ -11240,12 +11305,37 @@
       </c>
       <c r="D163" s="65" t="inlineStr">
         <is>
-          <t>BLA03, DMA02, DMA03, MA01, E01, E02, E03, E04, E05, E07, E08, E16b</t>
+          <t>BLA03 → B, E, F, I, L, M, O
+DMA02 → B, C, L, M, N
+DMA03 → G, H, J, O
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, K
+E05 → M, N
+E07 → F
+E08 → F, M
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E163" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA03, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA03, E03, E16b
+F Business Data validation – PASS → BLA03, E03, E07, E08, E16b
+G Business line manager name – PASS → DMA03, E03
+H Business line manager approval dates – PASS → DMA03, E03
+I DIV Test procedures listed within the Test results document – PASS → BLA03, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → DMA03
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA03, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA03, DMA02, E03, E05, E08
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05
+O Business Line Approval of Results – PASS → BLA03, DMA03, E03</t>
         </is>
       </c>
       <c r="F163" s="65" t="inlineStr">
@@ -11259,7 +11349,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="124" customHeight="1" s="73">
+    <row r="164" ht="282" customHeight="1" s="73">
       <c r="A164" s="70" t="inlineStr">
         <is>
           <t>1903</t>
@@ -11277,12 +11367,39 @@
       </c>
       <c r="D164" s="65" t="inlineStr">
         <is>
-          <t>BLA02, BLA03, DMA02, DMA03, DMA05, MA01, E01, E02, E03, E04, E05, E07, E08, E16b</t>
+          <t>BLA02 → B, E, F, I, L, M, O
+BLA03 → B, E, F, I, L, M, O
+DMA02 → B, C, G, H, J, L, M, N, O
+DMA03 → G, H, J, O
+DMA05 → G, H, J, O
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, E, F, G, H, K
+E05 → M, N
+E07 → F
+E08 → F, M
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E164" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA02, BLA03, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA02, BLA03, E03, E04, E16b
+F Business Data validation – PASS → BLA02, BLA03, E03, E04, E07, E08, E16b
+G Business line manager name – PASS → DMA02, DMA03, DMA05, E03, E04
+H Business line manager approval dates – PASS → DMA02, DMA03, DMA05, E03, E04
+I DIV Test procedures listed within the Test results document – PASS → BLA02, BLA03, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → DMA02, DMA03, DMA05
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA02, BLA03, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA02, BLA03, DMA02, E03, E05, E08
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05
+O Business Line Approval of Results – PASS → BLA02, BLA03, DMA02, DMA03, DMA05, E03</t>
         </is>
       </c>
       <c r="F164" s="65" t="inlineStr">
@@ -11296,7 +11413,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="124" customHeight="1" s="73">
+    <row r="165" ht="246" customHeight="1" s="73">
       <c r="A165" s="70" t="inlineStr">
         <is>
           <t>1917</t>
@@ -11314,12 +11431,36 @@
       </c>
       <c r="D165" s="65" t="inlineStr">
         <is>
-          <t>BLA05, BLA06, DMA02, MA01, E01, E02, E03, E04, E05, E10, E16b</t>
+          <t>BLA05 → B, E, F, I, L, M, O
+BLA06 → G, H, J, O
+DMA02 → B, C, L, M, N
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, K
+E05 → M, N
+E10 → M
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E165" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA05, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA05, E03, E16b
+F Business Data validation – PASS → BLA05, E03, E16b
+G Business line manager name – PASS → BLA06, E03
+H Business line manager approval dates – PASS → BLA06, E03
+I DIV Test procedures listed within the Test results document – PASS → BLA05, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → BLA06
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA05, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA05, DMA02, E03, E05, E10
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05
+O Business Line Approval of Results – PASS → BLA05, BLA06, E03</t>
         </is>
       </c>
       <c r="F165" s="65" t="inlineStr">
@@ -11333,7 +11474,7 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="124" customHeight="1" s="73">
+    <row r="166" ht="270" customHeight="1" s="73">
       <c r="A166" s="70" t="inlineStr">
         <is>
           <t>1936</t>
@@ -11351,12 +11492,38 @@
       </c>
       <c r="D166" s="65" t="inlineStr">
         <is>
-          <t>BLA03, BLA04, DMA02, DMA04, MA01, E01, E02, E03, E04, E05, E07, E08, E16b</t>
+          <t>BLA03 → B, E, F, I, L, M, O
+BLA04 → B, E, F, I, L, M, O
+DMA02 → B, C, G, H, J, L, M, N, O
+DMA04 → G, H, J, O
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, E, F, G, H, K
+E05 → M, N
+E07 → F
+E08 → F, M
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E166" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA03, BLA04, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA03, BLA04, E03, E04, E16b
+F Business Data validation – PASS → BLA03, BLA04, E03, E04, E07, E08, E16b
+G Business line manager name – PASS → DMA02, DMA04, E03, E04
+H Business line manager approval dates – PASS → DMA02, DMA04, E03, E04
+I DIV Test procedures listed within the Test results document – PASS → BLA03, BLA04, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → DMA02, DMA04
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA03, BLA04, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA03, BLA04, DMA02, E03, E05, E08
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05
+O Business Line Approval of Results – PASS → BLA03, BLA04, DMA02, DMA04, E03</t>
         </is>
       </c>
       <c r="F166" s="65" t="inlineStr">
@@ -11370,7 +11537,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="124" customHeight="1" s="73">
+    <row r="167" ht="378" customHeight="1" s="73">
       <c r="A167" s="70" t="inlineStr">
         <is>
           <t>1937</t>
@@ -11388,12 +11555,54 @@
       </c>
       <c r="D167" s="65" t="inlineStr">
         <is>
-          <t>BLA01, BLA02, BLA03, BLA04, BLA05, BLA06, DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12, MA01, E01, E02, E03, E04, E05, E07, E08, E09, E10, E16b</t>
+          <t>BLA01 → B, E, F, I, L, M, O
+BLA02 → B, E, F, I, L, M, O
+BLA03 → B, E, F, I, L, M, O
+BLA04 → B, E, F, I, L, M, O
+BLA05 → B, E, F, I, L, M, O
+BLA06 → G, H, J, O
+DMA01 → G, H, J, O
+DMA02 → B, C, G, H, J, L, M, N, O
+DMA03 → G, H, J, O
+DMA04 → G, H, J, O
+DMA05 → G, H, J, O
+DMA06 → G, H, J, O
+DMA07 → G, H, J, O
+DMA08 → G, H, J, O
+DMA09 → G, H, J, O
+DMA10 → G, H, J, O
+DMA11 → G, H, J, O
+DMA12 → G, H, J, O
+MA01 → D, K, N
+E01 → D, B, C, K, L, N
+E02 → D, K, N
+E03 → D, B, C, E, F, G, H, I, K, L, M, O
+E04 → D, E, F, G, H, K
+E05 → M, N
+E07 → F
+E08 → F, M
+E09 → G, H, J, O
+E10 → M
+E16b → D, B, E, F, I, K</t>
         </is>
       </c>
       <c r="E167" s="65" t="inlineStr">
         <is>
-          <t>14/14 PASS – D Application Name; B IT DR exercise name; C IT DR exercise name, was the excercise annually executed?; E Business Tester; F Business Data validation; G Business line manager name; H Business line manager approval dates; I DIV Test procedures listed within the Test results document; J Emails showing Business line manager approval of DIV testing results; K All evidence of Data Integrity DR test in BCIC; L Annual Testing Executed; M Data Integrity Validation Performed by IT DR Team; N Applications in Scope Identified; O Business Line Approval of Results</t>
+          <t>14/14 PASS
+D Application Name – PASS → MA01, E01, E02, E03, E04, E16b
+B IT DR exercise name – PASS → BLA01, BLA02, BLA03, BLA04, BLA05, DMA02, E01, E03, E16b
+C IT DR exercise name, was the excercise annually executed? – PASS → DMA02, E01, E03
+E Business Tester – PASS → BLA01, BLA02, BLA03, BLA04, BLA05, E03, E04, E16b
+F Business Data validation – PASS → BLA01, BLA02, BLA03, BLA04, BLA05, E03, E04, E07, E08, E16b
+G Business line manager name – PASS → BLA06, DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12, E03, E04, E09
+H Business line manager approval dates – PASS → BLA06, DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12, E03, E04, E09
+I DIV Test procedures listed within the Test results document – PASS → BLA01, BLA02, BLA03, BLA04, BLA05, E03, E16b
+J Emails showing Business line manager approval of DIV testing results – PASS → BLA06, DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12, E09
+K All evidence of Data Integrity DR test in BCIC – PASS → MA01, E01, E02, E03, E04, E16b
+L Annual Testing Executed – PASS → BLA01, BLA02, BLA03, BLA04, BLA05, DMA02, E01, E03
+M Data Integrity Validation Performed by IT DR Team – PASS → BLA01, BLA02, BLA03, BLA04, BLA05, DMA02, E03, E05, E08, E10
+N Applications in Scope Identified – PASS → DMA02, MA01, E01, E02, E05
+O Business Line Approval of Results – PASS → BLA01, BLA02, BLA03, BLA04, BLA05, BLA06, DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12, E03, E09</t>
         </is>
       </c>
       <c r="F167" s="65" t="inlineStr">
@@ -11818,7 +12027,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="60" customHeight="1" s="73">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -13483,7 +13691,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15.5" customHeight="1" s="73">
       <c r="A16" s="26" t="inlineStr">
         <is>

--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -239,6 +239,12 @@
     <font>
       <name val="Carlito"/>
       <b val="1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
       <color rgb="FF0563C1"/>
       <sz val="10"/>
       <u val="single"/>
@@ -534,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -752,6 +758,9 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="10" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1256,6 +1265,36 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>BSI.IT.6.C7.3</author>
+  </authors>
+  <commentList>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>Click an evidence file path to open the file. Keep this workbook in the same folder as the 'BSI.IT.6.C7.3-Evidences' folder (e.g. both in the same SharePoint / network / local folder) so the links resolve.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>BSI.IT.6.C7.3</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>Click an evidence file path to open the file. Keep this workbook in the same folder as the 'BSI.IT.6.C7.3-Evidences' folder (e.g. both in the same SharePoint / network / local folder) so the links resolve.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScopePopulationTable" displayName="ScopePopulationTable" ref="A4:H14" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="8">
@@ -6102,7 +6141,7 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B23" s="65" t="inlineStr">
+      <c r="B23" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
         </is>
@@ -6239,7 +6278,7 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B27" s="65" t="inlineStr">
+      <c r="B27" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
@@ -6384,7 +6423,7 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B32" s="65" t="inlineStr">
+      <c r="B32" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
@@ -6527,7 +6566,7 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B36" s="65" t="inlineStr">
+      <c r="B36" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
@@ -6675,7 +6714,7 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B40" s="65" t="inlineStr">
+      <c r="B40" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
@@ -6853,7 +6892,7 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B44" s="65" t="inlineStr">
+      <c r="B44" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
@@ -7031,7 +7070,7 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B48" s="65" t="inlineStr">
+      <c r="B48" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
@@ -7164,7 +7203,7 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B52" s="65" t="inlineStr">
+      <c r="B52" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
@@ -7274,7 +7313,7 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B53" s="65" t="inlineStr">
+      <c r="B53" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
@@ -7317,7 +7356,7 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B54" s="65" t="inlineStr">
+      <c r="B54" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
@@ -7359,7 +7398,7 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B55" s="65" t="inlineStr">
+      <c r="B55" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
@@ -7400,7 +7439,7 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B56" s="65" t="inlineStr">
+      <c r="B56" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
@@ -7491,7 +7530,7 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B60" s="65" t="inlineStr">
+      <c r="B60" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
@@ -7619,7 +7658,7 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B64" s="65" t="inlineStr">
+      <c r="B64" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
@@ -7758,7 +7797,7 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B68" s="65" t="inlineStr">
+      <c r="B68" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
@@ -7911,7 +7950,7 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B72" s="65" t="inlineStr">
+      <c r="B72" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
         </is>
@@ -8048,7 +8087,7 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B76" s="65" t="inlineStr">
+      <c r="B76" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
@@ -8188,7 +8227,7 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B77" s="65" t="inlineStr">
+      <c r="B77" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
@@ -8231,7 +8270,7 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B78" s="65" t="inlineStr">
+      <c r="B78" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
@@ -8273,7 +8312,7 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B79" s="65" t="inlineStr">
+      <c r="B79" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
@@ -8314,7 +8353,7 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B80" s="65" t="inlineStr">
+      <c r="B80" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
@@ -8400,7 +8439,7 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B84" s="65" t="inlineStr">
+      <c r="B84" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
         </is>
@@ -8437,7 +8476,7 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B85" s="65" t="inlineStr">
+      <c r="B85" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
         </is>
@@ -8474,7 +8513,7 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B86" s="65" t="inlineStr">
+      <c r="B86" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
         </is>
@@ -8511,7 +8550,7 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B87" s="65" t="inlineStr">
+      <c r="B87" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
         </is>
@@ -8548,7 +8587,7 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B88" s="65" t="inlineStr">
+      <c r="B88" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
         </is>
@@ -8585,7 +8624,7 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B89" s="65" t="inlineStr">
+      <c r="B89" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
@@ -8667,7 +8706,7 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B93" s="65" t="inlineStr">
+      <c r="B93" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
@@ -8704,7 +8743,7 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B94" s="65" t="inlineStr">
+      <c r="B94" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
@@ -8741,7 +8780,7 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B95" s="65" t="inlineStr">
+      <c r="B95" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
@@ -8778,7 +8817,7 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B96" s="65" t="inlineStr">
+      <c r="B96" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
@@ -8815,7 +8854,7 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B97" s="65" t="inlineStr">
+      <c r="B97" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
@@ -8852,7 +8891,7 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B98" s="65" t="inlineStr">
+      <c r="B98" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
@@ -8889,7 +8928,7 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B99" s="65" t="inlineStr">
+      <c r="B99" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
@@ -8926,7 +8965,7 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B100" s="65" t="inlineStr">
+      <c r="B100" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
         </is>
@@ -8963,7 +9002,7 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B101" s="65" t="inlineStr">
+      <c r="B101" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
@@ -9000,7 +9039,7 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B102" s="65" t="inlineStr">
+      <c r="B102" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
         </is>
@@ -9037,7 +9076,7 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B103" s="65" t="inlineStr">
+      <c r="B103" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
         </is>
@@ -9074,7 +9113,7 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B104" s="65" t="inlineStr">
+      <c r="B104" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
         </is>
@@ -9111,7 +9150,7 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B105" s="65" t="inlineStr">
+      <c r="B105" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
         </is>
@@ -9193,7 +9232,7 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B109" s="65" t="inlineStr">
+      <c r="B109" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
         </is>
@@ -9230,7 +9269,7 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B110" s="65" t="inlineStr">
+      <c r="B110" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
@@ -9267,7 +9306,7 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B111" s="65" t="inlineStr">
+      <c r="B111" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
@@ -9304,7 +9343,7 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B112" s="65" t="inlineStr">
+      <c r="B112" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
@@ -9341,7 +9380,7 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B113" s="65" t="inlineStr">
+      <c r="B113" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
@@ -9378,7 +9417,7 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B114" s="65" t="inlineStr">
+      <c r="B114" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
@@ -9415,7 +9454,7 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B115" s="65" t="inlineStr">
+      <c r="B115" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
@@ -9452,7 +9491,7 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B116" s="65" t="inlineStr">
+      <c r="B116" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
@@ -9489,7 +9528,7 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B117" s="65" t="inlineStr">
+      <c r="B117" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
@@ -9526,7 +9565,7 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B118" s="65" t="inlineStr">
+      <c r="B118" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
@@ -9563,7 +9602,7 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B119" s="65" t="inlineStr">
+      <c r="B119" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
@@ -9600,7 +9639,7 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B120" s="65" t="inlineStr">
+      <c r="B120" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
@@ -9682,7 +9721,7 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B124" s="65" t="inlineStr">
+      <c r="B124" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
         </is>
@@ -9725,7 +9764,7 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B125" s="65" t="inlineStr">
+      <c r="B125" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
         </is>
@@ -9768,7 +9807,7 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B126" s="65" t="inlineStr">
+      <c r="B126" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
         </is>
@@ -9811,7 +9850,7 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B127" s="65" t="inlineStr">
+      <c r="B127" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
         </is>
@@ -9854,7 +9893,7 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B128" s="65" t="inlineStr">
+      <c r="B128" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
         </is>
@@ -9897,7 +9936,7 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B129" s="65" t="inlineStr">
+      <c r="B129" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
@@ -9937,7 +9976,7 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B130" s="65" t="inlineStr">
+      <c r="B130" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
@@ -9977,7 +10016,7 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B131" s="65" t="inlineStr">
+      <c r="B131" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
@@ -10022,7 +10061,7 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B132" s="65" t="inlineStr">
+      <c r="B132" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
@@ -10062,7 +10101,7 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B133" s="65" t="inlineStr">
+      <c r="B133" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
@@ -10102,7 +10141,7 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B134" s="65" t="inlineStr">
+      <c r="B134" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
@@ -10142,7 +10181,7 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B135" s="65" t="inlineStr">
+      <c r="B135" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
@@ -10182,7 +10221,7 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B136" s="65" t="inlineStr">
+      <c r="B136" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
@@ -10222,7 +10261,7 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B137" s="65" t="inlineStr">
+      <c r="B137" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
         </is>
@@ -10262,7 +10301,7 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B138" s="65" t="inlineStr">
+      <c r="B138" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
@@ -10302,7 +10341,7 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B139" s="65" t="inlineStr">
+      <c r="B139" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
         </is>
@@ -10342,7 +10381,7 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B140" s="65" t="inlineStr">
+      <c r="B140" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
         </is>
@@ -10382,7 +10421,7 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B141" s="65" t="inlineStr">
+      <c r="B141" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
         </is>
@@ -10422,7 +10461,7 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B142" s="65" t="inlineStr">
+      <c r="B142" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
         </is>
@@ -10459,7 +10498,7 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B143" s="65" t="inlineStr">
+      <c r="B143" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
         </is>
@@ -10498,7 +10537,7 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B144" s="65" t="inlineStr">
+      <c r="B144" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
@@ -10540,7 +10579,7 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B145" s="65" t="inlineStr">
+      <c r="B145" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
@@ -10579,7 +10618,7 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B146" s="65" t="inlineStr">
+      <c r="B146" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
@@ -10627,7 +10666,7 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B147" s="65" t="inlineStr">
+      <c r="B147" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
@@ -10669,7 +10708,7 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B148" s="65" t="inlineStr">
+      <c r="B148" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
@@ -10707,7 +10746,7 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B149" s="65" t="inlineStr">
+      <c r="B149" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
@@ -10744,7 +10783,7 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B150" s="65" t="inlineStr">
+      <c r="B150" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
@@ -10782,7 +10821,7 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B151" s="65" t="inlineStr">
+      <c r="B151" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
@@ -10825,7 +10864,7 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B152" s="65" t="inlineStr">
+      <c r="B152" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
@@ -10862,7 +10901,7 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B153" s="65" t="inlineStr">
+      <c r="B153" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
@@ -10899,7 +10938,7 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B154" s="65" t="inlineStr">
+      <c r="B154" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
@@ -11782,6 +11821,7 @@
     <hyperlink ref="B18" location="'Application Attribute Testing'!A122" display="Evidence reference table – evidence number → attribute tests"/>
     <hyperlink ref="B19" location="'Application Attribute Testing'!A156" display="Conclusion – all applications in scope (PASS) with evidence references"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" tooltip="Open evidence file" r:id="rId1"/>
     <hyperlink ref="H23" location="'Application Attribute Testing'!A109" display="MA01"/>
     <hyperlink ref="I23" location="'Application Attribute Testing'!A110" display="E01"/>
     <hyperlink ref="J23" location="'Application Attribute Testing'!A111" display="E02"/>
@@ -11789,6 +11829,7 @@
     <hyperlink ref="L23" location="'Application Attribute Testing'!A113" display="E04"/>
     <hyperlink ref="M23" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" tooltip="Open evidence file" r:id="rId2"/>
     <hyperlink ref="H27" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I27" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J27" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11799,6 +11840,7 @@
     <hyperlink ref="O27" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="P27" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" tooltip="Open evidence file" r:id="rId3"/>
     <hyperlink ref="H32" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I32" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J32" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11809,6 +11851,7 @@
     <hyperlink ref="O32" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="P32" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A36" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" tooltip="Open evidence file" r:id="rId4"/>
     <hyperlink ref="H36" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I36" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J36" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11820,6 +11863,7 @@
     <hyperlink ref="P36" location="'Application Attribute Testing'!A116" display="E08"/>
     <hyperlink ref="Q36" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A40" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" tooltip="Open evidence file" r:id="rId5"/>
     <hyperlink ref="H40" location="'Application Attribute Testing'!A89" display="BLA06"/>
     <hyperlink ref="I40" location="'Application Attribute Testing'!A93" display="DMA01"/>
     <hyperlink ref="J40" location="'Application Attribute Testing'!A94" display="DMA02"/>
@@ -11837,6 +11881,7 @@
     <hyperlink ref="V40" location="'Application Attribute Testing'!A113" display="E04"/>
     <hyperlink ref="W40" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A44" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" tooltip="Open evidence file" r:id="rId6"/>
     <hyperlink ref="H44" location="'Application Attribute Testing'!A89" display="BLA06"/>
     <hyperlink ref="I44" location="'Application Attribute Testing'!A93" display="DMA01"/>
     <hyperlink ref="J44" location="'Application Attribute Testing'!A94" display="DMA02"/>
@@ -11854,6 +11899,7 @@
     <hyperlink ref="V44" location="'Application Attribute Testing'!A113" display="E04"/>
     <hyperlink ref="W44" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A48" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" tooltip="Open evidence file" r:id="rId7"/>
     <hyperlink ref="H48" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I48" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J48" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11862,6 +11908,7 @@
     <hyperlink ref="M48" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="N48" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A52" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" tooltip="Open evidence file" r:id="rId8"/>
     <hyperlink ref="H52" location="'Application Attribute Testing'!A89" display="BLA06"/>
     <hyperlink ref="I52" location="'Application Attribute Testing'!A93" display="DMA01"/>
     <hyperlink ref="J52" location="'Application Attribute Testing'!A94" display="DMA02"/>
@@ -11877,10 +11924,15 @@
     <hyperlink ref="T52" location="'Application Attribute Testing'!A104" display="DMA12"/>
     <hyperlink ref="U52" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A53" location="'Application Attribute Testing'!A93" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" tooltip="Open evidence file" r:id="rId9"/>
     <hyperlink ref="A54" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" tooltip="Open evidence file" r:id="rId10"/>
     <hyperlink ref="A55" location="'Application Attribute Testing'!A95" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" tooltip="Open evidence file" r:id="rId11"/>
     <hyperlink ref="A56" location="'Application Attribute Testing'!A96" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" tooltip="Open evidence file" r:id="rId12"/>
     <hyperlink ref="A60" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" tooltip="Open evidence file" r:id="rId13"/>
     <hyperlink ref="H60" location="'Application Attribute Testing'!A109" display="MA01"/>
     <hyperlink ref="I60" location="'Application Attribute Testing'!A110" display="E01"/>
     <hyperlink ref="J60" location="'Application Attribute Testing'!A111" display="E02"/>
@@ -11888,6 +11940,7 @@
     <hyperlink ref="L60" location="'Application Attribute Testing'!A113" display="E04"/>
     <hyperlink ref="M60" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A64" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" tooltip="Open evidence file" r:id="rId14"/>
     <hyperlink ref="H64" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I64" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J64" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11897,6 +11950,7 @@
     <hyperlink ref="N64" location="'Application Attribute Testing'!A110" display="E01"/>
     <hyperlink ref="O64" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="A68" location="'Application Attribute Testing'!A114" display="E05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" tooltip="Open evidence file" r:id="rId15"/>
     <hyperlink ref="H68" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I68" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J68" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11909,6 +11963,7 @@
     <hyperlink ref="Q68" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="R68" location="'Application Attribute Testing'!A118" display="E10"/>
     <hyperlink ref="A72" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" tooltip="Open evidence file" r:id="rId16"/>
     <hyperlink ref="H72" location="'Application Attribute Testing'!A94" display="DMA02"/>
     <hyperlink ref="I72" location="'Application Attribute Testing'!A109" display="MA01"/>
     <hyperlink ref="J72" location="'Application Attribute Testing'!A110" display="E01"/>
@@ -11916,6 +11971,7 @@
     <hyperlink ref="L72" location="'Application Attribute Testing'!A114" display="E05"/>
     <hyperlink ref="M72" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A76" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" tooltip="Open evidence file" r:id="rId17"/>
     <hyperlink ref="H76" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I76" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J76" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11937,40 +11993,106 @@
     <hyperlink ref="Z76" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="AA76" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A77" location="'Application Attribute Testing'!A93" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" tooltip="Open evidence file" r:id="rId18"/>
     <hyperlink ref="A78" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" tooltip="Open evidence file" r:id="rId19"/>
     <hyperlink ref="A79" location="'Application Attribute Testing'!A95" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" tooltip="Open evidence file" r:id="rId20"/>
     <hyperlink ref="A80" location="'Application Attribute Testing'!A96" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" tooltip="Open evidence file" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" tooltip="Open evidence file" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" tooltip="Open evidence file" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" tooltip="Open evidence file" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" tooltip="Open evidence file" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" tooltip="Open evidence file" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" tooltip="Open evidence file" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" tooltip="Open evidence file" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" tooltip="Open evidence file" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" tooltip="Open evidence file" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" tooltip="Open evidence file" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" tooltip="Open evidence file" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" tooltip="Open evidence file" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" tooltip="Open evidence file" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" tooltip="Open evidence file" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" tooltip="Open evidence file" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" tooltip="Open evidence file" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" tooltip="Open evidence file" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" tooltip="Open evidence file" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" tooltip="Open evidence file" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" tooltip="Open evidence file" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" tooltip="Open evidence file" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" tooltip="Open evidence file" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" tooltip="Open evidence file" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" tooltip="Open evidence file" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" tooltip="Open evidence file" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" tooltip="Open evidence file" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" tooltip="Open evidence file" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" tooltip="Open evidence file" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" tooltip="Open evidence file" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" tooltip="Open evidence file" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" tooltip="Open evidence file" r:id="rId52"/>
     <hyperlink ref="A124" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" tooltip="Open evidence file" r:id="rId53"/>
     <hyperlink ref="A125" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" tooltip="Open evidence file" r:id="rId54"/>
     <hyperlink ref="A126" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" tooltip="Open evidence file" r:id="rId55"/>
     <hyperlink ref="A127" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" tooltip="Open evidence file" r:id="rId56"/>
     <hyperlink ref="A128" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" tooltip="Open evidence file" r:id="rId57"/>
     <hyperlink ref="A129" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" tooltip="Open evidence file" r:id="rId58"/>
     <hyperlink ref="A130" location="'Application Attribute Testing'!A93" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" tooltip="Open evidence file" r:id="rId59"/>
     <hyperlink ref="A131" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" tooltip="Open evidence file" r:id="rId60"/>
     <hyperlink ref="A132" location="'Application Attribute Testing'!A95" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" tooltip="Open evidence file" r:id="rId61"/>
     <hyperlink ref="A133" location="'Application Attribute Testing'!A96" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" tooltip="Open evidence file" r:id="rId62"/>
     <hyperlink ref="A134" location="'Application Attribute Testing'!A97" display="DMA05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" tooltip="Open evidence file" r:id="rId63"/>
     <hyperlink ref="A135" location="'Application Attribute Testing'!A98" display="DMA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" tooltip="Open evidence file" r:id="rId64"/>
     <hyperlink ref="A136" location="'Application Attribute Testing'!A99" display="DMA07"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" tooltip="Open evidence file" r:id="rId65"/>
     <hyperlink ref="A137" location="'Application Attribute Testing'!A100" display="DMA08"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" tooltip="Open evidence file" r:id="rId66"/>
     <hyperlink ref="A138" location="'Application Attribute Testing'!A101" display="DMA09"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" tooltip="Open evidence file" r:id="rId67"/>
     <hyperlink ref="A139" location="'Application Attribute Testing'!A102" display="DMA10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" tooltip="Open evidence file" r:id="rId68"/>
     <hyperlink ref="A140" location="'Application Attribute Testing'!A103" display="DMA11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" tooltip="Open evidence file" r:id="rId69"/>
     <hyperlink ref="A141" location="'Application Attribute Testing'!A104" display="DMA12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" tooltip="Open evidence file" r:id="rId70"/>
     <hyperlink ref="A142" location="'Application Attribute Testing'!A105" display="DMA13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" tooltip="Open evidence file" r:id="rId71"/>
     <hyperlink ref="A143" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" tooltip="Open evidence file" r:id="rId72"/>
     <hyperlink ref="A144" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" tooltip="Open evidence file" r:id="rId73"/>
     <hyperlink ref="A145" location="'Application Attribute Testing'!A111" display="E02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" tooltip="Open evidence file" r:id="rId74"/>
     <hyperlink ref="A146" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" tooltip="Open evidence file" r:id="rId75"/>
     <hyperlink ref="A147" location="'Application Attribute Testing'!A113" display="E04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" tooltip="Open evidence file" r:id="rId76"/>
     <hyperlink ref="A148" location="'Application Attribute Testing'!A114" display="E05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" tooltip="Open evidence file" r:id="rId77"/>
     <hyperlink ref="A149" location="'Application Attribute Testing'!A115" display="E07"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" tooltip="Open evidence file" r:id="rId78"/>
     <hyperlink ref="A150" location="'Application Attribute Testing'!A116" display="E08"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" tooltip="Open evidence file" r:id="rId79"/>
     <hyperlink ref="A151" location="'Application Attribute Testing'!A117" display="E09"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" tooltip="Open evidence file" r:id="rId80"/>
     <hyperlink ref="A152" location="'Application Attribute Testing'!A118" display="E10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" tooltip="Open evidence file" r:id="rId81"/>
     <hyperlink ref="A153" location="'Application Attribute Testing'!A119" display="E13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" tooltip="Open evidence file" r:id="rId82"/>
     <hyperlink ref="A154" location="'Application Attribute Testing'!A120" display="E16b"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" tooltip="Open evidence file" r:id="rId83"/>
     <hyperlink ref="A158" location="'Application Attribute Testing-1'!A3" display="1822"/>
     <hyperlink ref="B158" location="'Application Attribute Testing-1'!A3" display="ACH Express"/>
     <hyperlink ref="A159" location="'Application Attribute Testing-1'!A4" display="1867"/>
@@ -11994,6 +12116,7 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -13876,12 +13999,12 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="92" t="inlineStr">
         <is>
           <t>MA01_BSI In-Scope Applications-2026.png</t>
         </is>
       </c>
-      <c r="C3" s="35" t="inlineStr">
+      <c r="C3" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications</t>
         </is>
@@ -13930,12 +14053,12 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="92" t="inlineStr">
         <is>
           <t>BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
@@ -13984,12 +14107,12 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="92" t="inlineStr">
         <is>
           <t>BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
@@ -14038,12 +14161,12 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="92" t="inlineStr">
         <is>
           <t>BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
@@ -14092,12 +14215,12 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="92" t="inlineStr">
         <is>
           <t>BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
@@ -14146,12 +14269,12 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="92" t="inlineStr">
         <is>
           <t>BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
@@ -14200,12 +14323,12 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="92" t="inlineStr">
         <is>
           <t>BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
@@ -14254,12 +14377,12 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="92" t="inlineStr">
         <is>
           <t>DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14308,12 +14431,12 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="92" t="inlineStr">
         <is>
           <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14362,12 +14485,12 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="92" t="inlineStr">
         <is>
           <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14416,12 +14539,12 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="92" t="inlineStr">
         <is>
           <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14470,12 +14593,12 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="92" t="inlineStr">
         <is>
           <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14524,12 +14647,12 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="92" t="inlineStr">
         <is>
           <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14578,12 +14701,12 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="92" t="inlineStr">
         <is>
           <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14632,12 +14755,12 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="92" t="inlineStr">
         <is>
           <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14686,12 +14809,12 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="92" t="inlineStr">
         <is>
           <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14740,12 +14863,12 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="92" t="inlineStr">
         <is>
           <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14794,12 +14917,12 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="92" t="inlineStr">
         <is>
           <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14848,12 +14971,12 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="92" t="inlineStr">
         <is>
           <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14902,12 +15025,12 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="92" t="inlineStr">
         <is>
           <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
@@ -14956,12 +15079,12 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15010,12 +15133,12 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15064,12 +15187,12 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15118,12 +15241,12 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15172,12 +15295,12 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15226,12 +15349,12 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15280,12 +15403,12 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15334,12 +15457,12 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15388,12 +15511,12 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15442,12 +15565,12 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="C32" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -15496,12 +15619,12 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B33" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
-      <c r="C33" s="35" t="inlineStr">
+      <c r="C33" s="92" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
@@ -17250,38 +17373,101 @@
   <autoFilter ref="A2:K33"/>
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing'!A109" display="MA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" tooltip="Open evidence file" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" tooltip="Open evidence folder" r:id="rId2"/>
     <hyperlink ref="A4" location="'Application Attribute Testing'!A84" display="BLA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" tooltip="Open evidence file" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" tooltip="Open evidence folder" r:id="rId4"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A85" display="BLA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" tooltip="Open evidence file" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" tooltip="Open evidence folder" r:id="rId6"/>
     <hyperlink ref="A6" location="'Application Attribute Testing'!A86" display="BLA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" tooltip="Open evidence file" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" tooltip="Open evidence folder" r:id="rId8"/>
     <hyperlink ref="A7" location="'Application Attribute Testing'!A87" display="BLA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" tooltip="Open evidence file" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" tooltip="Open evidence folder" r:id="rId10"/>
     <hyperlink ref="A8" location="'Application Attribute Testing'!A88" display="BLA05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" tooltip="Open evidence file" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" tooltip="Open evidence folder" r:id="rId12"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A89" display="BLA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" tooltip="Open evidence file" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" tooltip="Open evidence folder" r:id="rId14"/>
     <hyperlink ref="A10" location="'Application Attribute Testing'!A93" display="DMA01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" tooltip="Open evidence file" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" tooltip="Open evidence folder" r:id="rId16"/>
     <hyperlink ref="A11" location="'Application Attribute Testing'!A94" display="DMA02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" tooltip="Open evidence file" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" tooltip="Open evidence folder" r:id="rId18"/>
     <hyperlink ref="A12" location="'Application Attribute Testing'!A95" display="DMA03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" tooltip="Open evidence file" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" tooltip="Open evidence folder" r:id="rId20"/>
     <hyperlink ref="A13" location="'Application Attribute Testing'!A96" display="DMA04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" tooltip="Open evidence file" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" tooltip="Open evidence folder" r:id="rId22"/>
     <hyperlink ref="A14" location="'Application Attribute Testing'!A97" display="DMA05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" tooltip="Open evidence file" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" tooltip="Open evidence folder" r:id="rId24"/>
     <hyperlink ref="A15" location="'Application Attribute Testing'!A98" display="DMA06"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" tooltip="Open evidence file" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" tooltip="Open evidence folder" r:id="rId26"/>
     <hyperlink ref="A16" location="'Application Attribute Testing'!A99" display="DMA07"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" tooltip="Open evidence file" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" tooltip="Open evidence folder" r:id="rId28"/>
     <hyperlink ref="A17" location="'Application Attribute Testing'!A100" display="DMA08"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" tooltip="Open evidence file" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" tooltip="Open evidence folder" r:id="rId30"/>
     <hyperlink ref="A18" location="'Application Attribute Testing'!A101" display="DMA09"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" tooltip="Open evidence file" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" tooltip="Open evidence folder" r:id="rId32"/>
     <hyperlink ref="A19" location="'Application Attribute Testing'!A102" display="DMA10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" tooltip="Open evidence file" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" tooltip="Open evidence folder" r:id="rId34"/>
     <hyperlink ref="A20" location="'Application Attribute Testing'!A103" display="DMA11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" tooltip="Open evidence file" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" tooltip="Open evidence folder" r:id="rId36"/>
     <hyperlink ref="A21" location="'Application Attribute Testing'!A104" display="DMA12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" tooltip="Open evidence file" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" tooltip="Open evidence folder" r:id="rId38"/>
     <hyperlink ref="A22" location="'Application Attribute Testing'!A105" display="DMA13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" tooltip="Open evidence file" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" tooltip="Open evidence folder" r:id="rId40"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A110" display="E01"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" tooltip="Open evidence file" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" tooltip="Open evidence folder" r:id="rId42"/>
     <hyperlink ref="A24" location="'Application Attribute Testing'!A111" display="E02"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" tooltip="Open evidence file" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" tooltip="Open evidence folder" r:id="rId44"/>
     <hyperlink ref="A25" location="'Application Attribute Testing'!A112" display="E03"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" tooltip="Open evidence file" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" tooltip="Open evidence folder" r:id="rId46"/>
     <hyperlink ref="A26" location="'Application Attribute Testing'!A113" display="E04"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" tooltip="Open evidence file" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" tooltip="Open evidence folder" r:id="rId48"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A114" display="E05"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" tooltip="Open evidence file" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" tooltip="Open evidence folder" r:id="rId50"/>
     <hyperlink ref="A28" location="'Application Attribute Testing'!A115" display="E07"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" tooltip="Open evidence file" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" tooltip="Open evidence folder" r:id="rId52"/>
     <hyperlink ref="A29" location="'Application Attribute Testing'!A116" display="E08"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" tooltip="Open evidence file" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" tooltip="Open evidence folder" r:id="rId54"/>
     <hyperlink ref="A30" location="'Application Attribute Testing'!A117" display="E09"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" tooltip="Open evidence file" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" tooltip="Open evidence folder" r:id="rId56"/>
     <hyperlink ref="A31" location="'Application Attribute Testing'!A118" display="E10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" tooltip="Open evidence file" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" tooltip="Open evidence folder" r:id="rId58"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A119" display="E13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" tooltip="Open evidence file" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" tooltip="Open evidence folder" r:id="rId60"/>
     <hyperlink ref="A33" location="'Application Attribute Testing'!A120" display="E16b"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" tooltip="Open evidence file" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" tooltip="Open evidence folder" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION.xlsx
@@ -15,6 +15,8 @@
     <sheet name="DR 2024 Testing Results" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="EvidenceFolder">'WP Summary'!$B$27</definedName>
+    <definedName name="EvidenceRoot">IF(LEN(TRIM(EvidenceFolder))=0,LEFT(CELL("filename",'WP Summary'!$A$1),FIND("[",CELL("filename",'WP Summary'!$A$1))-1)&amp;"BSI.IT.6.C7.3-Evidences"&amp;IF(LEFT(LEFT(CELL("filename",'WP Summary'!$A$1),FIND("[",CELL("filename",'WP Summary'!$A$1))-1),4)="http","/","\"),TRIM(EvidenceFolder)&amp;IF(OR(RIGHT(TRIM(EvidenceFolder),1)="\",RIGHT(TRIM(EvidenceFolder),1)="/"),"",IF(LEFT(TRIM(EvidenceFolder),4)="http","/","\")))</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BSI.IT.6.C7.3 Evidence Index'!$A$2:$K$33</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -26,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -249,8 +251,18 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -361,8 +373,13 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -536,11 +553,55 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -762,6 +823,16 @@
     <xf numFmtId="0" fontId="38" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1271,9 +1342,9 @@
     <author>BSI.IT.6.C7.3</author>
   </authors>
   <commentList>
-    <comment ref="B22" authorId="0" shapeId="0">
+    <comment ref="B27" authorId="0" shapeId="0">
       <text>
-        <t>Click an evidence file path to open the file. Keep this workbook in the same folder as the 'BSI.IT.6.C7.3-Evidences' folder (e.g. both in the same SharePoint / network / local folder) so the links resolve.</t>
+        <t>Leave blank if the folder 'BSI.IT.6.C7.3-Evidences' is saved next to this workbook. Otherwise paste the full path of the BSI.IT.6.C7.3-Evidences folder, e.g. C:\Audit\BSI.IT.6.C7.3-Evidences  or  \\server\share\BSI.IT.6.C7.3-Evidences  or  https://tenant.sharepoint.com/sites/Audit/Shared Documents/BSI.IT.6.C7.3-Evidences</t>
       </text>
     </comment>
   </commentList>
@@ -1286,9 +1357,24 @@
     <author>BSI.IT.6.C7.3</author>
   </authors>
   <commentList>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>Click an evidence file path to open the file. The evidence folder location is set on tab 'WP Summary' (yellow cell, row 27): blank = folder 'BSI.IT.6.C7.3-Evidences' next to this workbook.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>BSI.IT.6.C7.3</author>
+  </authors>
+  <commentList>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
-        <t>Click an evidence file path to open the file. Keep this workbook in the same folder as the 'BSI.IT.6.C7.3-Evidences' folder (e.g. both in the same SharePoint / network / local folder) so the links resolve.</t>
+        <t>Click an evidence file path to open the file. The evidence folder location is set on tab 'WP Summary' (yellow cell, row 27): blank = folder 'BSI.IT.6.C7.3-Evidences' next to this workbook.</t>
       </text>
     </comment>
   </commentList>
@@ -1529,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" style="73" min="1" max="1"/>
@@ -2053,12 +2139,58 @@
     <row r="22" ht="27.15" customHeight="1" s="73"/>
     <row r="23" ht="20.5" customHeight="1" s="73"/>
     <row r="24" ht="20.5" customHeight="1" s="73"/>
+    <row r="26">
+      <c r="A26" s="93" t="inlineStr">
+        <is>
+          <t>Evidence file links – setting (clicking an evidence file path opens the file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" s="73">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>Evidence folder</t>
+        </is>
+      </c>
+      <c r="B27" s="95" t="n"/>
+      <c r="C27" s="99" t="n"/>
+      <c r="D27" s="99" t="n"/>
+      <c r="E27" s="100" t="n"/>
+      <c r="F27" s="96" t="inlineStr">
+        <is>
+          <t>← Yellow cell: leave blank if the evidence folder sits next to this workbook; otherwise paste its full path (local, network or SharePoint).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>Links resolve to</t>
+        </is>
+      </c>
+      <c r="B28" s="97">
+        <f>EvidenceRoot</f>
+        <v/>
+      </c>
+      <c r="C28" s="99" t="n"/>
+      <c r="D28" s="99" t="n"/>
+      <c r="E28" s="100" t="n"/>
+      <c r="F28" s="98">
+        <f>HYPERLINK(EvidenceRoot,"▶ Test: open the evidence folder")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="9">
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A21:H24"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -2069,6 +2201,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6141,10 +6274,9 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B23" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
-        </is>
+      <c r="B23" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
+        <v/>
       </c>
       <c r="C23" s="65" t="inlineStr">
         <is>
@@ -6278,10 +6410,9 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B27" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
-        </is>
+      <c r="B27" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <v/>
       </c>
       <c r="C27" s="65" t="inlineStr">
         <is>
@@ -6423,10 +6554,9 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B32" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
+      <c r="B32" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
       </c>
       <c r="C32" s="65" t="inlineStr">
         <is>
@@ -6566,10 +6696,9 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B36" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
+      <c r="B36" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
       </c>
       <c r="C36" s="65" t="inlineStr">
         <is>
@@ -6714,10 +6843,9 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B40" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
+      <c r="B40" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
       </c>
       <c r="C40" s="65" t="inlineStr">
         <is>
@@ -6892,10 +7020,9 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B44" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
+      <c r="B44" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
       </c>
       <c r="C44" s="65" t="inlineStr">
         <is>
@@ -7070,10 +7197,9 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B48" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
+      <c r="B48" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
       </c>
       <c r="C48" s="65" t="inlineStr">
         <is>
@@ -7203,10 +7329,9 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B52" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
-        </is>
+      <c r="B52" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
+        <v/>
       </c>
       <c r="C52" s="65" t="inlineStr">
         <is>
@@ -7313,10 +7438,9 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B53" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
-        </is>
+      <c r="B53" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C53" s="65" t="inlineStr">
         <is>
@@ -7356,10 +7480,9 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B54" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
-        </is>
+      <c r="B54" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
+        <v/>
       </c>
       <c r="C54" s="65" t="inlineStr">
         <is>
@@ -7398,10 +7521,9 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B55" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
-        </is>
+      <c r="B55" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C55" s="65" t="inlineStr">
         <is>
@@ -7439,10 +7561,9 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B56" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
-        </is>
+      <c r="B56" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <v/>
       </c>
       <c r="C56" s="65" t="inlineStr">
         <is>
@@ -7530,10 +7651,9 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B60" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
+      <c r="B60" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
       </c>
       <c r="C60" s="65" t="inlineStr">
         <is>
@@ -7658,10 +7778,9 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B64" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
-        </is>
+      <c r="B64" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <v/>
       </c>
       <c r="C64" s="65" t="inlineStr">
         <is>
@@ -7797,10 +7916,9 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B68" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
-        </is>
+      <c r="B68" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
+        <v/>
       </c>
       <c r="C68" s="65" t="inlineStr">
         <is>
@@ -7950,10 +8068,9 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B72" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
-        </is>
+      <c r="B72" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
+        <v/>
       </c>
       <c r="C72" s="65" t="inlineStr">
         <is>
@@ -8087,10 +8204,9 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B76" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
-        </is>
+      <c r="B76" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
+        <v/>
       </c>
       <c r="C76" s="65" t="inlineStr">
         <is>
@@ -8227,10 +8343,9 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B77" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
-        </is>
+      <c r="B77" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C77" s="65" t="inlineStr">
         <is>
@@ -8270,10 +8385,9 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B78" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
-        </is>
+      <c r="B78" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
+        <v/>
       </c>
       <c r="C78" s="65" t="inlineStr">
         <is>
@@ -8312,10 +8426,9 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B79" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
-        </is>
+      <c r="B79" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C79" s="65" t="inlineStr">
         <is>
@@ -8353,10 +8466,9 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B80" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
-        </is>
+      <c r="B80" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <v/>
       </c>
       <c r="C80" s="65" t="inlineStr">
         <is>
@@ -8439,10 +8551,9 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B84" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
-        </is>
+      <c r="B84" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
       </c>
       <c r="C84" s="65" t="inlineStr">
         <is>
@@ -8476,10 +8587,9 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B85" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
-        </is>
+      <c r="B85" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
       </c>
       <c r="C85" s="65" t="inlineStr">
         <is>
@@ -8513,10 +8623,9 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B86" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
-        </is>
+      <c r="B86" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
       </c>
       <c r="C86" s="65" t="inlineStr">
         <is>
@@ -8550,10 +8659,9 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B87" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
-        </is>
+      <c r="B87" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
+        <v/>
       </c>
       <c r="C87" s="65" t="inlineStr">
         <is>
@@ -8587,10 +8695,9 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B88" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
-        </is>
+      <c r="B88" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
       </c>
       <c r="C88" s="65" t="inlineStr">
         <is>
@@ -8624,10 +8731,9 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B89" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
-        </is>
+      <c r="B89" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
+        <v/>
       </c>
       <c r="C89" s="65" t="inlineStr">
         <is>
@@ -8706,10 +8812,9 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B93" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
-        </is>
+      <c r="B93" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C93" s="65" t="inlineStr">
         <is>
@@ -8743,10 +8848,9 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B94" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
-        </is>
+      <c r="B94" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
+        <v/>
       </c>
       <c r="C94" s="65" t="inlineStr">
         <is>
@@ -8780,10 +8884,9 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B95" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
-        </is>
+      <c r="B95" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C95" s="65" t="inlineStr">
         <is>
@@ -8817,10 +8920,9 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B96" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
-        </is>
+      <c r="B96" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <v/>
       </c>
       <c r="C96" s="65" t="inlineStr">
         <is>
@@ -8854,10 +8956,9 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B97" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
-        </is>
+      <c r="B97" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
+        <v/>
       </c>
       <c r="C97" s="65" t="inlineStr">
         <is>
@@ -8891,10 +8992,9 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B98" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
-        </is>
+      <c r="B98" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C98" s="65" t="inlineStr">
         <is>
@@ -8928,10 +9028,9 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B99" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
-        </is>
+      <c r="B99" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C99" s="65" t="inlineStr">
         <is>
@@ -8965,10 +9064,9 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B100" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
-        </is>
+      <c r="B100" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C100" s="65" t="inlineStr">
         <is>
@@ -9002,10 +9100,9 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B101" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
-        </is>
+      <c r="B101" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C101" s="65" t="inlineStr">
         <is>
@@ -9039,10 +9136,9 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B102" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
-        </is>
+      <c r="B102" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
+        <v/>
       </c>
       <c r="C102" s="65" t="inlineStr">
         <is>
@@ -9076,10 +9172,9 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B103" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
-        </is>
+      <c r="B103" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
+        <v/>
       </c>
       <c r="C103" s="65" t="inlineStr">
         <is>
@@ -9113,10 +9208,9 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B104" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
-        </is>
+      <c r="B104" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
+        <v/>
       </c>
       <c r="C104" s="65" t="inlineStr">
         <is>
@@ -9150,10 +9244,9 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B105" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
-        </is>
+      <c r="B105" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
+        <v/>
       </c>
       <c r="C105" s="65" t="inlineStr">
         <is>
@@ -9232,10 +9325,9 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B109" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
-        </is>
+      <c r="B109" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
+        <v/>
       </c>
       <c r="C109" s="65" t="inlineStr">
         <is>
@@ -9269,10 +9361,9 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B110" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
-        </is>
+      <c r="B110" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <v/>
       </c>
       <c r="C110" s="65" t="inlineStr">
         <is>
@@ -9306,10 +9397,9 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B111" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
-        </is>
+      <c r="B111" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
+        <v/>
       </c>
       <c r="C111" s="65" t="inlineStr">
         <is>
@@ -9343,10 +9433,9 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B112" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
+      <c r="B112" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
       </c>
       <c r="C112" s="65" t="inlineStr">
         <is>
@@ -9380,10 +9469,9 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B113" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
-        </is>
+      <c r="B113" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
+        <v/>
       </c>
       <c r="C113" s="65" t="inlineStr">
         <is>
@@ -9417,10 +9505,9 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B114" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
-        </is>
+      <c r="B114" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
+        <v/>
       </c>
       <c r="C114" s="65" t="inlineStr">
         <is>
@@ -9454,10 +9541,9 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B115" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
-        </is>
+      <c r="B115" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
+        <v/>
       </c>
       <c r="C115" s="65" t="inlineStr">
         <is>
@@ -9491,10 +9577,9 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B116" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
-        </is>
+      <c r="B116" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
+        <v/>
       </c>
       <c r="C116" s="65" t="inlineStr">
         <is>
@@ -9528,10 +9613,9 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B117" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
-        </is>
+      <c r="B117" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
+        <v/>
       </c>
       <c r="C117" s="65" t="inlineStr">
         <is>
@@ -9565,10 +9649,9 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B118" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
-        </is>
+      <c r="B118" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
+        <v/>
       </c>
       <c r="C118" s="65" t="inlineStr">
         <is>
@@ -9602,10 +9685,9 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B119" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
-        </is>
+      <c r="B119" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
+        <v/>
       </c>
       <c r="C119" s="65" t="inlineStr">
         <is>
@@ -9639,10 +9721,9 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B120" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
-        </is>
+      <c r="B120" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
+        <v/>
       </c>
       <c r="C120" s="65" t="inlineStr">
         <is>
@@ -9721,10 +9802,9 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B124" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
-        </is>
+      <c r="B124" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
       </c>
       <c r="C124" s="65" t="inlineStr">
         <is>
@@ -9764,10 +9844,9 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B125" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
-        </is>
+      <c r="B125" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
       </c>
       <c r="C125" s="65" t="inlineStr">
         <is>
@@ -9807,10 +9886,9 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B126" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
-        </is>
+      <c r="B126" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
       </c>
       <c r="C126" s="65" t="inlineStr">
         <is>
@@ -9850,10 +9928,9 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B127" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
-        </is>
+      <c r="B127" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
+        <v/>
       </c>
       <c r="C127" s="65" t="inlineStr">
         <is>
@@ -9893,10 +9970,9 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B128" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
-        </is>
+      <c r="B128" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
       </c>
       <c r="C128" s="65" t="inlineStr">
         <is>
@@ -9936,10 +10012,9 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B129" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
-        </is>
+      <c r="B129" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
+        <v/>
       </c>
       <c r="C129" s="65" t="inlineStr">
         <is>
@@ -9976,10 +10051,9 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B130" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
-        </is>
+      <c r="B130" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C130" s="65" t="inlineStr">
         <is>
@@ -10016,10 +10090,9 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B131" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
-        </is>
+      <c r="B131" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
+        <v/>
       </c>
       <c r="C131" s="65" t="inlineStr">
         <is>
@@ -10061,10 +10134,9 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B132" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
-        </is>
+      <c r="B132" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C132" s="65" t="inlineStr">
         <is>
@@ -10101,10 +10173,9 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B133" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
-        </is>
+      <c r="B133" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <v/>
       </c>
       <c r="C133" s="65" t="inlineStr">
         <is>
@@ -10141,10 +10212,9 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B134" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
-        </is>
+      <c r="B134" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
+        <v/>
       </c>
       <c r="C134" s="65" t="inlineStr">
         <is>
@@ -10181,10 +10251,9 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B135" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
-        </is>
+      <c r="B135" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C135" s="65" t="inlineStr">
         <is>
@@ -10221,10 +10290,9 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B136" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
-        </is>
+      <c r="B136" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C136" s="65" t="inlineStr">
         <is>
@@ -10261,10 +10329,9 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B137" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
-        </is>
+      <c r="B137" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C137" s="65" t="inlineStr">
         <is>
@@ -10301,10 +10368,9 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B138" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
-        </is>
+      <c r="B138" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
+        <v/>
       </c>
       <c r="C138" s="65" t="inlineStr">
         <is>
@@ -10341,10 +10407,9 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B139" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
-        </is>
+      <c r="B139" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
+        <v/>
       </c>
       <c r="C139" s="65" t="inlineStr">
         <is>
@@ -10381,10 +10446,9 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B140" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
-        </is>
+      <c r="B140" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
+        <v/>
       </c>
       <c r="C140" s="65" t="inlineStr">
         <is>
@@ -10421,10 +10485,9 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B141" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
-        </is>
+      <c r="B141" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
+        <v/>
       </c>
       <c r="C141" s="65" t="inlineStr">
         <is>
@@ -10461,10 +10524,9 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B142" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
-        </is>
+      <c r="B142" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
+        <v/>
       </c>
       <c r="C142" s="65" t="inlineStr">
         <is>
@@ -10498,10 +10560,9 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B143" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
-        </is>
+      <c r="B143" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
+        <v/>
       </c>
       <c r="C143" s="65" t="inlineStr">
         <is>
@@ -10537,10 +10598,9 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B144" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
-        </is>
+      <c r="B144" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <v/>
       </c>
       <c r="C144" s="65" t="inlineStr">
         <is>
@@ -10579,10 +10639,9 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B145" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
-        </is>
+      <c r="B145" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
+        <v/>
       </c>
       <c r="C145" s="65" t="inlineStr">
         <is>
@@ -10618,10 +10677,9 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B146" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
+      <c r="B146" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
       </c>
       <c r="C146" s="65" t="inlineStr">
         <is>
@@ -10666,10 +10724,9 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B147" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
-        </is>
+      <c r="B147" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
+        <v/>
       </c>
       <c r="C147" s="65" t="inlineStr">
         <is>
@@ -10708,10 +10765,9 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B148" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
-        </is>
+      <c r="B148" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
+        <v/>
       </c>
       <c r="C148" s="65" t="inlineStr">
         <is>
@@ -10746,10 +10802,9 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B149" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
-        </is>
+      <c r="B149" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
+        <v/>
       </c>
       <c r="C149" s="65" t="inlineStr">
         <is>
@@ -10783,10 +10838,9 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B150" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
-        </is>
+      <c r="B150" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
+        <v/>
       </c>
       <c r="C150" s="65" t="inlineStr">
         <is>
@@ -10821,10 +10875,9 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B151" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
-        </is>
+      <c r="B151" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
+        <v/>
       </c>
       <c r="C151" s="65" t="inlineStr">
         <is>
@@ -10864,10 +10917,9 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B152" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
-        </is>
+      <c r="B152" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
+        <v/>
       </c>
       <c r="C152" s="65" t="inlineStr">
         <is>
@@ -10901,10 +10953,9 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B153" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
-        </is>
+      <c r="B153" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
+        <v/>
       </c>
       <c r="C153" s="65" t="inlineStr">
         <is>
@@ -10938,10 +10989,9 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B154" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
-        </is>
+      <c r="B154" s="64">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
+        <v/>
       </c>
       <c r="C154" s="65" t="inlineStr">
         <is>
@@ -11821,7 +11871,6 @@
     <hyperlink ref="B18" location="'Application Attribute Testing'!A122" display="Evidence reference table – evidence number → attribute tests"/>
     <hyperlink ref="B19" location="'Application Attribute Testing'!A156" display="Conclusion – all applications in scope (PASS) with evidence references"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A109" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" tooltip="Open evidence file" r:id="rId1"/>
     <hyperlink ref="H23" location="'Application Attribute Testing'!A109" display="MA01"/>
     <hyperlink ref="I23" location="'Application Attribute Testing'!A110" display="E01"/>
     <hyperlink ref="J23" location="'Application Attribute Testing'!A111" display="E02"/>
@@ -11829,7 +11878,6 @@
     <hyperlink ref="L23" location="'Application Attribute Testing'!A113" display="E04"/>
     <hyperlink ref="M23" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A110" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" tooltip="Open evidence file" r:id="rId2"/>
     <hyperlink ref="H27" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I27" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J27" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11840,7 +11888,6 @@
     <hyperlink ref="O27" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="P27" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A112" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" tooltip="Open evidence file" r:id="rId3"/>
     <hyperlink ref="H32" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I32" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J32" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11851,7 +11898,6 @@
     <hyperlink ref="O32" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="P32" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A36" location="'Application Attribute Testing'!A112" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" tooltip="Open evidence file" r:id="rId4"/>
     <hyperlink ref="H36" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I36" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J36" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11863,7 +11909,6 @@
     <hyperlink ref="P36" location="'Application Attribute Testing'!A116" display="E08"/>
     <hyperlink ref="Q36" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A40" location="'Application Attribute Testing'!A112" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" tooltip="Open evidence file" r:id="rId5"/>
     <hyperlink ref="H40" location="'Application Attribute Testing'!A89" display="BLA06"/>
     <hyperlink ref="I40" location="'Application Attribute Testing'!A93" display="DMA01"/>
     <hyperlink ref="J40" location="'Application Attribute Testing'!A94" display="DMA02"/>
@@ -11881,7 +11926,6 @@
     <hyperlink ref="V40" location="'Application Attribute Testing'!A113" display="E04"/>
     <hyperlink ref="W40" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A44" location="'Application Attribute Testing'!A112" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" tooltip="Open evidence file" r:id="rId6"/>
     <hyperlink ref="H44" location="'Application Attribute Testing'!A89" display="BLA06"/>
     <hyperlink ref="I44" location="'Application Attribute Testing'!A93" display="DMA01"/>
     <hyperlink ref="J44" location="'Application Attribute Testing'!A94" display="DMA02"/>
@@ -11899,7 +11943,6 @@
     <hyperlink ref="V44" location="'Application Attribute Testing'!A113" display="E04"/>
     <hyperlink ref="W44" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A48" location="'Application Attribute Testing'!A112" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" tooltip="Open evidence file" r:id="rId7"/>
     <hyperlink ref="H48" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I48" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J48" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11908,7 +11951,6 @@
     <hyperlink ref="M48" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="N48" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A52" location="'Application Attribute Testing'!A89" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" tooltip="Open evidence file" r:id="rId8"/>
     <hyperlink ref="H52" location="'Application Attribute Testing'!A89" display="BLA06"/>
     <hyperlink ref="I52" location="'Application Attribute Testing'!A93" display="DMA01"/>
     <hyperlink ref="J52" location="'Application Attribute Testing'!A94" display="DMA02"/>
@@ -11924,15 +11966,10 @@
     <hyperlink ref="T52" location="'Application Attribute Testing'!A104" display="DMA12"/>
     <hyperlink ref="U52" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A53" location="'Application Attribute Testing'!A93" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" tooltip="Open evidence file" r:id="rId9"/>
     <hyperlink ref="A54" location="'Application Attribute Testing'!A94" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" tooltip="Open evidence file" r:id="rId10"/>
     <hyperlink ref="A55" location="'Application Attribute Testing'!A95" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" tooltip="Open evidence file" r:id="rId11"/>
     <hyperlink ref="A56" location="'Application Attribute Testing'!A96" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" tooltip="Open evidence file" r:id="rId12"/>
     <hyperlink ref="A60" location="'Application Attribute Testing'!A112" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" tooltip="Open evidence file" r:id="rId13"/>
     <hyperlink ref="H60" location="'Application Attribute Testing'!A109" display="MA01"/>
     <hyperlink ref="I60" location="'Application Attribute Testing'!A110" display="E01"/>
     <hyperlink ref="J60" location="'Application Attribute Testing'!A111" display="E02"/>
@@ -11940,7 +11977,6 @@
     <hyperlink ref="L60" location="'Application Attribute Testing'!A113" display="E04"/>
     <hyperlink ref="M60" location="'Application Attribute Testing'!A120" display="E16b"/>
     <hyperlink ref="A64" location="'Application Attribute Testing'!A110" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" tooltip="Open evidence file" r:id="rId14"/>
     <hyperlink ref="H64" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I64" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J64" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11950,7 +11986,6 @@
     <hyperlink ref="N64" location="'Application Attribute Testing'!A110" display="E01"/>
     <hyperlink ref="O64" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="A68" location="'Application Attribute Testing'!A114" display="E05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" tooltip="Open evidence file" r:id="rId15"/>
     <hyperlink ref="H68" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I68" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J68" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11963,7 +11998,6 @@
     <hyperlink ref="Q68" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="R68" location="'Application Attribute Testing'!A118" display="E10"/>
     <hyperlink ref="A72" location="'Application Attribute Testing'!A109" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" tooltip="Open evidence file" r:id="rId16"/>
     <hyperlink ref="H72" location="'Application Attribute Testing'!A94" display="DMA02"/>
     <hyperlink ref="I72" location="'Application Attribute Testing'!A109" display="MA01"/>
     <hyperlink ref="J72" location="'Application Attribute Testing'!A110" display="E01"/>
@@ -11971,7 +12005,6 @@
     <hyperlink ref="L72" location="'Application Attribute Testing'!A114" display="E05"/>
     <hyperlink ref="M72" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A76" location="'Application Attribute Testing'!A89" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" tooltip="Open evidence file" r:id="rId17"/>
     <hyperlink ref="H76" location="'Application Attribute Testing'!A84" display="BLA01"/>
     <hyperlink ref="I76" location="'Application Attribute Testing'!A85" display="BLA02"/>
     <hyperlink ref="J76" location="'Application Attribute Testing'!A86" display="BLA03"/>
@@ -11993,106 +12026,40 @@
     <hyperlink ref="Z76" location="'Application Attribute Testing'!A112" display="E03"/>
     <hyperlink ref="AA76" location="'Application Attribute Testing'!A117" display="E09"/>
     <hyperlink ref="A77" location="'Application Attribute Testing'!A93" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" tooltip="Open evidence file" r:id="rId18"/>
     <hyperlink ref="A78" location="'Application Attribute Testing'!A94" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" tooltip="Open evidence file" r:id="rId19"/>
     <hyperlink ref="A79" location="'Application Attribute Testing'!A95" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" tooltip="Open evidence file" r:id="rId20"/>
     <hyperlink ref="A80" location="'Application Attribute Testing'!A96" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" tooltip="Open evidence file" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" tooltip="Open evidence file" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" tooltip="Open evidence file" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" tooltip="Open evidence file" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" tooltip="Open evidence file" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" tooltip="Open evidence file" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" tooltip="Open evidence file" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" tooltip="Open evidence file" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" tooltip="Open evidence file" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" tooltip="Open evidence file" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" tooltip="Open evidence file" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" tooltip="Open evidence file" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" tooltip="Open evidence file" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" tooltip="Open evidence file" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" tooltip="Open evidence file" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" tooltip="Open evidence file" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" tooltip="Open evidence file" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" tooltip="Open evidence file" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" tooltip="Open evidence file" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" tooltip="Open evidence file" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" tooltip="Open evidence file" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" tooltip="Open evidence file" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" tooltip="Open evidence file" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" tooltip="Open evidence file" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" tooltip="Open evidence file" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" tooltip="Open evidence file" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" tooltip="Open evidence file" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" tooltip="Open evidence file" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" tooltip="Open evidence file" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" tooltip="Open evidence file" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" tooltip="Open evidence file" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" tooltip="Open evidence file" r:id="rId52"/>
     <hyperlink ref="A124" location="'Application Attribute Testing'!A84" display="BLA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" tooltip="Open evidence file" r:id="rId53"/>
     <hyperlink ref="A125" location="'Application Attribute Testing'!A85" display="BLA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" tooltip="Open evidence file" r:id="rId54"/>
     <hyperlink ref="A126" location="'Application Attribute Testing'!A86" display="BLA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" tooltip="Open evidence file" r:id="rId55"/>
     <hyperlink ref="A127" location="'Application Attribute Testing'!A87" display="BLA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" tooltip="Open evidence file" r:id="rId56"/>
     <hyperlink ref="A128" location="'Application Attribute Testing'!A88" display="BLA05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" tooltip="Open evidence file" r:id="rId57"/>
     <hyperlink ref="A129" location="'Application Attribute Testing'!A89" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" tooltip="Open evidence file" r:id="rId58"/>
     <hyperlink ref="A130" location="'Application Attribute Testing'!A93" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" tooltip="Open evidence file" r:id="rId59"/>
     <hyperlink ref="A131" location="'Application Attribute Testing'!A94" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" tooltip="Open evidence file" r:id="rId60"/>
     <hyperlink ref="A132" location="'Application Attribute Testing'!A95" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" tooltip="Open evidence file" r:id="rId61"/>
     <hyperlink ref="A133" location="'Application Attribute Testing'!A96" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" tooltip="Open evidence file" r:id="rId62"/>
     <hyperlink ref="A134" location="'Application Attribute Testing'!A97" display="DMA05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" tooltip="Open evidence file" r:id="rId63"/>
     <hyperlink ref="A135" location="'Application Attribute Testing'!A98" display="DMA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" tooltip="Open evidence file" r:id="rId64"/>
     <hyperlink ref="A136" location="'Application Attribute Testing'!A99" display="DMA07"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" tooltip="Open evidence file" r:id="rId65"/>
     <hyperlink ref="A137" location="'Application Attribute Testing'!A100" display="DMA08"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" tooltip="Open evidence file" r:id="rId66"/>
     <hyperlink ref="A138" location="'Application Attribute Testing'!A101" display="DMA09"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" tooltip="Open evidence file" r:id="rId67"/>
     <hyperlink ref="A139" location="'Application Attribute Testing'!A102" display="DMA10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" tooltip="Open evidence file" r:id="rId68"/>
     <hyperlink ref="A140" location="'Application Attribute Testing'!A103" display="DMA11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" tooltip="Open evidence file" r:id="rId69"/>
     <hyperlink ref="A141" location="'Application Attribute Testing'!A104" display="DMA12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" tooltip="Open evidence file" r:id="rId70"/>
     <hyperlink ref="A142" location="'Application Attribute Testing'!A105" display="DMA13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" tooltip="Open evidence file" r:id="rId71"/>
     <hyperlink ref="A143" location="'Application Attribute Testing'!A109" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" tooltip="Open evidence file" r:id="rId72"/>
     <hyperlink ref="A144" location="'Application Attribute Testing'!A110" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" tooltip="Open evidence file" r:id="rId73"/>
     <hyperlink ref="A145" location="'Application Attribute Testing'!A111" display="E02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" tooltip="Open evidence file" r:id="rId74"/>
     <hyperlink ref="A146" location="'Application Attribute Testing'!A112" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" tooltip="Open evidence file" r:id="rId75"/>
     <hyperlink ref="A147" location="'Application Attribute Testing'!A113" display="E04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" tooltip="Open evidence file" r:id="rId76"/>
     <hyperlink ref="A148" location="'Application Attribute Testing'!A114" display="E05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" tooltip="Open evidence file" r:id="rId77"/>
     <hyperlink ref="A149" location="'Application Attribute Testing'!A115" display="E07"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" tooltip="Open evidence file" r:id="rId78"/>
     <hyperlink ref="A150" location="'Application Attribute Testing'!A116" display="E08"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" tooltip="Open evidence file" r:id="rId79"/>
     <hyperlink ref="A151" location="'Application Attribute Testing'!A117" display="E09"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" tooltip="Open evidence file" r:id="rId80"/>
     <hyperlink ref="A152" location="'Application Attribute Testing'!A118" display="E10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" tooltip="Open evidence file" r:id="rId81"/>
     <hyperlink ref="A153" location="'Application Attribute Testing'!A119" display="E13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" tooltip="Open evidence file" r:id="rId82"/>
     <hyperlink ref="A154" location="'Application Attribute Testing'!A120" display="E16b"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" tooltip="Open evidence file" r:id="rId83"/>
     <hyperlink ref="A158" location="'Application Attribute Testing-1'!A3" display="1822"/>
     <hyperlink ref="B158" location="'Application Attribute Testing-1'!A3" display="ACH Express"/>
     <hyperlink ref="A159" location="'Application Attribute Testing-1'!A4" display="1867"/>
@@ -13999,15 +13966,13 @@
           <t>MA01</t>
         </is>
       </c>
-      <c r="B3" s="92" t="inlineStr">
-        <is>
-          <t>MA01_BSI In-Scope Applications-2026.png</t>
-        </is>
-      </c>
-      <c r="C3" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications</t>
-        </is>
+      <c r="B3" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"MA01_BSI In-Scope Applications-2026.png")</f>
+        <v/>
+      </c>
+      <c r="C3" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications","\","/"),"01_Management_Attestation_In-Scope_Applications"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications")</f>
+        <v/>
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
@@ -14053,15 +14018,13 @@
           <t>BLA01</t>
         </is>
       </c>
-      <c r="B4" s="92" t="inlineStr">
-        <is>
-          <t>BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
-        </is>
-      </c>
-      <c r="C4" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
-        </is>
+      <c r="B4" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
+      </c>
+      <c r="C4" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
+        <v/>
       </c>
       <c r="D4" s="35" t="inlineStr">
         <is>
@@ -14107,15 +14070,13 @@
           <t>BLA02</t>
         </is>
       </c>
-      <c r="B5" s="92" t="inlineStr">
-        <is>
-          <t>BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
-        </is>
-      </c>
-      <c r="C5" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
-        </is>
+      <c r="B5" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
+      </c>
+      <c r="C5" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
+        <v/>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
@@ -14161,15 +14122,13 @@
           <t>BLA03</t>
         </is>
       </c>
-      <c r="B6" s="92" t="inlineStr">
-        <is>
-          <t>BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
-        </is>
-      </c>
-      <c r="C6" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
-        </is>
+      <c r="B6" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
+      </c>
+      <c r="C6" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
+        <v/>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
@@ -14215,15 +14174,13 @@
           <t>BLA04</t>
         </is>
       </c>
-      <c r="B7" s="92" t="inlineStr">
-        <is>
-          <t>BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
-        </is>
-      </c>
-      <c r="C7" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
-        </is>
+      <c r="B7" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
+        <v/>
+      </c>
+      <c r="C7" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
+        <v/>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
@@ -14269,15 +14226,13 @@
           <t>BLA05</t>
         </is>
       </c>
-      <c r="B8" s="92" t="inlineStr">
-        <is>
-          <t>BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
-        </is>
-      </c>
-      <c r="C8" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
-        </is>
+      <c r="B8" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
+      </c>
+      <c r="C8" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
+        <v/>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
@@ -14323,15 +14278,13 @@
           <t>BLA06</t>
         </is>
       </c>
-      <c r="B9" s="92" t="inlineStr">
-        <is>
-          <t>BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
-        </is>
-      </c>
-      <c r="C9" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
-        </is>
+      <c r="B9" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C9" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email","\","/"),"02_Business_Line_Approval_Results_Email"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email")</f>
+        <v/>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
@@ -14377,15 +14330,13 @@
           <t>DMA01</t>
         </is>
       </c>
-      <c r="B10" s="92" t="inlineStr">
-        <is>
-          <t>DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C10" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B10" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C10" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
@@ -14431,15 +14382,13 @@
           <t>DMA02</t>
         </is>
       </c>
-      <c r="B11" s="92" t="inlineStr">
-        <is>
-          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
-        </is>
-      </c>
-      <c r="C11" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B11" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C11" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
@@ -14485,15 +14434,13 @@
           <t>DMA03</t>
         </is>
       </c>
-      <c r="B12" s="92" t="inlineStr">
-        <is>
-          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C12" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B12" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C12" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
@@ -14539,15 +14486,13 @@
           <t>DMA04</t>
         </is>
       </c>
-      <c r="B13" s="92" t="inlineStr">
-        <is>
-          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
-        </is>
-      </c>
-      <c r="C13" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B13" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C13" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
@@ -14593,15 +14538,13 @@
           <t>DMA05</t>
         </is>
       </c>
-      <c r="B14" s="92" t="inlineStr">
-        <is>
-          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
-        </is>
-      </c>
-      <c r="C14" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B14" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C14" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
@@ -14647,15 +14590,13 @@
           <t>DMA06</t>
         </is>
       </c>
-      <c r="B15" s="92" t="inlineStr">
-        <is>
-          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C15" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B15" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C15" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
@@ -14701,15 +14642,13 @@
           <t>DMA07</t>
         </is>
       </c>
-      <c r="B16" s="92" t="inlineStr">
-        <is>
-          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C16" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B16" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C16" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
@@ -14755,15 +14694,13 @@
           <t>DMA08</t>
         </is>
       </c>
-      <c r="B17" s="92" t="inlineStr">
-        <is>
-          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C17" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B17" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C17" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
@@ -14809,15 +14746,13 @@
           <t>DMA09</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C18" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B18" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C18" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
@@ -14863,15 +14798,13 @@
           <t>DMA10</t>
         </is>
       </c>
-      <c r="B19" s="92" t="inlineStr">
-        <is>
-          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
-        </is>
-      </c>
-      <c r="C19" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B19" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
+        <v/>
+      </c>
+      <c r="C19" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D19" s="35" t="inlineStr">
         <is>
@@ -14917,15 +14850,13 @@
           <t>DMA11</t>
         </is>
       </c>
-      <c r="B20" s="92" t="inlineStr">
-        <is>
-          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
-        </is>
-      </c>
-      <c r="C20" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B20" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
+        <v/>
+      </c>
+      <c r="C20" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D20" s="35" t="inlineStr">
         <is>
@@ -14971,15 +14902,13 @@
           <t>DMA12</t>
         </is>
       </c>
-      <c r="B21" s="92" t="inlineStr">
-        <is>
-          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
-        </is>
-      </c>
-      <c r="C21" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B21" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
+        <v/>
+      </c>
+      <c r="C21" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D21" s="35" t="inlineStr">
         <is>
@@ -15025,15 +14954,13 @@
           <t>DMA13</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
-        </is>
-      </c>
-      <c r="C22" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
-        </is>
+      <c r="B22" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
+        <v/>
+      </c>
+      <c r="C22" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals","\","/"),"03_DIV_Manager_Attestation_Email_Approvals"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals")</f>
+        <v/>
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
@@ -15079,15 +15006,13 @@
           <t>E01</t>
         </is>
       </c>
-      <c r="B23" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
-        </is>
-      </c>
-      <c r="C23" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B23" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <v/>
+      </c>
+      <c r="C23" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
@@ -15133,15 +15058,13 @@
           <t>E02</t>
         </is>
       </c>
-      <c r="B24" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
-        </is>
-      </c>
-      <c r="C24" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B24" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
+        <v/>
+      </c>
+      <c r="C24" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
@@ -15187,15 +15110,13 @@
           <t>E03</t>
         </is>
       </c>
-      <c r="B25" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
-        </is>
-      </c>
-      <c r="C25" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B25" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
+      </c>
+      <c r="C25" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
@@ -15241,15 +15162,13 @@
           <t>E04</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
-        </is>
-      </c>
-      <c r="C26" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B26" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
+        <v/>
+      </c>
+      <c r="C26" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
@@ -15295,15 +15214,13 @@
           <t>E05</t>
         </is>
       </c>
-      <c r="B27" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
-        </is>
-      </c>
-      <c r="C27" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B27" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
+        <v/>
+      </c>
+      <c r="C27" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
@@ -15349,15 +15266,13 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="B28" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
-        </is>
-      </c>
-      <c r="C28" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B28" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
+        <v/>
+      </c>
+      <c r="C28" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
@@ -15403,15 +15318,13 @@
           <t>E08</t>
         </is>
       </c>
-      <c r="B29" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
-        </is>
-      </c>
-      <c r="C29" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B29" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
+        <v/>
+      </c>
+      <c r="C29" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
@@ -15457,15 +15370,13 @@
           <t>E09</t>
         </is>
       </c>
-      <c r="B30" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
-        </is>
-      </c>
-      <c r="C30" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B30" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
+        <v/>
+      </c>
+      <c r="C30" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D30" s="35" t="inlineStr">
         <is>
@@ -15511,15 +15422,13 @@
           <t>E10</t>
         </is>
       </c>
-      <c r="B31" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
-        </is>
-      </c>
-      <c r="C31" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B31" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
+        <v/>
+      </c>
+      <c r="C31" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D31" s="35" t="inlineStr">
         <is>
@@ -15565,15 +15474,13 @@
           <t>E13</t>
         </is>
       </c>
-      <c r="B32" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
-        </is>
-      </c>
-      <c r="C32" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B32" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
+        <v/>
+      </c>
+      <c r="C32" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D32" s="35" t="inlineStr">
         <is>
@@ -15619,15 +15526,13 @@
           <t>E16b</t>
         </is>
       </c>
-      <c r="B33" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
-        </is>
-      </c>
-      <c r="C33" s="92" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
+      <c r="B33" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
+        <v/>
+      </c>
+      <c r="C33" s="92">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence")</f>
+        <v/>
       </c>
       <c r="D33" s="35" t="inlineStr">
         <is>
@@ -17373,98 +17278,36 @@
   <autoFilter ref="A2:K33"/>
   <hyperlinks>
     <hyperlink ref="A3" location="'Application Attribute Testing'!A109" display="MA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" tooltip="Open evidence file" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" tooltip="Open evidence folder" r:id="rId2"/>
     <hyperlink ref="A4" location="'Application Attribute Testing'!A84" display="BLA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" tooltip="Open evidence file" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" tooltip="Open evidence folder" r:id="rId4"/>
     <hyperlink ref="A5" location="'Application Attribute Testing'!A85" display="BLA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" tooltip="Open evidence file" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" tooltip="Open evidence folder" r:id="rId6"/>
     <hyperlink ref="A6" location="'Application Attribute Testing'!A86" display="BLA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" tooltip="Open evidence file" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" tooltip="Open evidence folder" r:id="rId8"/>
     <hyperlink ref="A7" location="'Application Attribute Testing'!A87" display="BLA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" tooltip="Open evidence file" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" tooltip="Open evidence folder" r:id="rId10"/>
     <hyperlink ref="A8" location="'Application Attribute Testing'!A88" display="BLA05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" tooltip="Open evidence file" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" tooltip="Open evidence folder" r:id="rId12"/>
     <hyperlink ref="A9" location="'Application Attribute Testing'!A89" display="BLA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" tooltip="Open evidence file" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" tooltip="Open evidence folder" r:id="rId14"/>
     <hyperlink ref="A10" location="'Application Attribute Testing'!A93" display="DMA01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" tooltip="Open evidence file" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" tooltip="Open evidence folder" r:id="rId16"/>
     <hyperlink ref="A11" location="'Application Attribute Testing'!A94" display="DMA02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" tooltip="Open evidence file" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" tooltip="Open evidence folder" r:id="rId18"/>
     <hyperlink ref="A12" location="'Application Attribute Testing'!A95" display="DMA03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" tooltip="Open evidence file" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" tooltip="Open evidence folder" r:id="rId20"/>
     <hyperlink ref="A13" location="'Application Attribute Testing'!A96" display="DMA04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" tooltip="Open evidence file" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" tooltip="Open evidence folder" r:id="rId22"/>
     <hyperlink ref="A14" location="'Application Attribute Testing'!A97" display="DMA05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" tooltip="Open evidence file" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" tooltip="Open evidence folder" r:id="rId24"/>
     <hyperlink ref="A15" location="'Application Attribute Testing'!A98" display="DMA06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" tooltip="Open evidence file" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" tooltip="Open evidence folder" r:id="rId26"/>
     <hyperlink ref="A16" location="'Application Attribute Testing'!A99" display="DMA07"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" tooltip="Open evidence file" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" tooltip="Open evidence folder" r:id="rId28"/>
     <hyperlink ref="A17" location="'Application Attribute Testing'!A100" display="DMA08"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" tooltip="Open evidence file" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" tooltip="Open evidence folder" r:id="rId30"/>
     <hyperlink ref="A18" location="'Application Attribute Testing'!A101" display="DMA09"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" tooltip="Open evidence file" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" tooltip="Open evidence folder" r:id="rId32"/>
     <hyperlink ref="A19" location="'Application Attribute Testing'!A102" display="DMA10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" tooltip="Open evidence file" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" tooltip="Open evidence folder" r:id="rId34"/>
     <hyperlink ref="A20" location="'Application Attribute Testing'!A103" display="DMA11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" tooltip="Open evidence file" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" tooltip="Open evidence folder" r:id="rId36"/>
     <hyperlink ref="A21" location="'Application Attribute Testing'!A104" display="DMA12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" tooltip="Open evidence file" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" tooltip="Open evidence folder" r:id="rId38"/>
     <hyperlink ref="A22" location="'Application Attribute Testing'!A105" display="DMA13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" tooltip="Open evidence file" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" tooltip="Open evidence folder" r:id="rId40"/>
     <hyperlink ref="A23" location="'Application Attribute Testing'!A110" display="E01"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" tooltip="Open evidence file" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" tooltip="Open evidence folder" r:id="rId42"/>
     <hyperlink ref="A24" location="'Application Attribute Testing'!A111" display="E02"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" tooltip="Open evidence file" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" tooltip="Open evidence folder" r:id="rId44"/>
     <hyperlink ref="A25" location="'Application Attribute Testing'!A112" display="E03"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" tooltip="Open evidence file" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" tooltip="Open evidence folder" r:id="rId46"/>
     <hyperlink ref="A26" location="'Application Attribute Testing'!A113" display="E04"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" tooltip="Open evidence file" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" tooltip="Open evidence folder" r:id="rId48"/>
     <hyperlink ref="A27" location="'Application Attribute Testing'!A114" display="E05"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" tooltip="Open evidence file" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" tooltip="Open evidence folder" r:id="rId50"/>
     <hyperlink ref="A28" location="'Application Attribute Testing'!A115" display="E07"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" tooltip="Open evidence file" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" tooltip="Open evidence folder" r:id="rId52"/>
     <hyperlink ref="A29" location="'Application Attribute Testing'!A116" display="E08"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" tooltip="Open evidence file" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" tooltip="Open evidence folder" r:id="rId54"/>
     <hyperlink ref="A30" location="'Application Attribute Testing'!A117" display="E09"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" tooltip="Open evidence file" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" tooltip="Open evidence folder" r:id="rId56"/>
     <hyperlink ref="A31" location="'Application Attribute Testing'!A118" display="E10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" tooltip="Open evidence file" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" tooltip="Open evidence folder" r:id="rId58"/>
     <hyperlink ref="A32" location="'Application Attribute Testing'!A119" display="E13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" tooltip="Open evidence file" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" tooltip="Open evidence folder" r:id="rId60"/>
     <hyperlink ref="A33" location="'Application Attribute Testing'!A120" display="E16b"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" tooltip="Open evidence file" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" tooltip="Open evidence folder" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
